--- a/research/traditional_assets/database/data/romania/romania_real_estate_general_diversified.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_real_estate_general_diversified.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08408489620091836</v>
+        <v>0.08398816036699688</v>
       </c>
       <c r="C2">
-        <v>15.65795706322744</v>
+        <v>15.52010594387862</v>
       </c>
       <c r="D2">
-        <v>12.71795706322744</v>
+        <v>12.73390594387862</v>
       </c>
       <c r="E2">
-        <v>-1.78</v>
+        <v>-1.6262</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1538</v>
       </c>
       <c r="G2">
         <v>2.94</v>
@@ -1439,28 +1439,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.007736139999999999</v>
       </c>
       <c r="N2">
-        <v>0.7150000000000001</v>
+        <v>0.7072638600000001</v>
       </c>
       <c r="O2">
-        <v>0.1144</v>
+        <v>0.1131622176</v>
       </c>
       <c r="P2">
-        <v>0.6006</v>
+        <v>0.5941016424000001</v>
       </c>
       <c r="Q2">
-        <v>0.9756</v>
+        <v>0.9691016424000001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08408489620091836</v>
+        <v>0.0844097377444413</v>
       </c>
       <c r="T2">
-        <v>0.5270060068313374</v>
+        <v>0.5314775729499063</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>92.42335324851931</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08398816036699688</v>
+        <v>0.08389142453307542</v>
       </c>
       <c r="C3">
-        <v>15.52010594387862</v>
+        <v>15.38229487595951</v>
       </c>
       <c r="D3">
-        <v>12.73390594387862</v>
+        <v>12.74989487595952</v>
       </c>
       <c r="E3">
-        <v>-1.6262</v>
+        <v>-1.4724</v>
       </c>
       <c r="F3">
-        <v>0.1538</v>
+        <v>0.3076</v>
       </c>
       <c r="G3">
         <v>2.94</v>
@@ -1521,28 +1521,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M3">
-        <v>0.007736139999999999</v>
+        <v>0.01547228</v>
       </c>
       <c r="N3">
-        <v>0.7072638600000001</v>
+        <v>0.6995277200000001</v>
       </c>
       <c r="O3">
-        <v>0.1131622176</v>
+        <v>0.1119244352</v>
       </c>
       <c r="P3">
-        <v>0.5941016424000001</v>
+        <v>0.5876032848</v>
       </c>
       <c r="Q3">
-        <v>0.9691016424000001</v>
+        <v>0.9626032848</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0844097377444413</v>
+        <v>0.08474120870721982</v>
       </c>
       <c r="T3">
-        <v>0.5314775729499063</v>
+        <v>0.5360403955198746</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>92.42335324851931</v>
+        <v>46.21167662425965</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08389142453307542</v>
+        <v>0.08379468869915395</v>
       </c>
       <c r="C4">
-        <v>15.38229487595951</v>
+        <v>15.2445240105278</v>
       </c>
       <c r="D4">
-        <v>12.74989487595952</v>
+        <v>12.7659240105278</v>
       </c>
       <c r="E4">
-        <v>-1.4724</v>
+        <v>-1.3186</v>
       </c>
       <c r="F4">
-        <v>0.3076</v>
+        <v>0.4614</v>
       </c>
       <c r="G4">
         <v>2.94</v>
@@ -1603,28 +1603,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M4">
-        <v>0.01547228</v>
+        <v>0.02320842</v>
       </c>
       <c r="N4">
-        <v>0.6995277200000001</v>
+        <v>0.6917915800000001</v>
       </c>
       <c r="O4">
-        <v>0.1119244352</v>
+        <v>0.1106866528</v>
       </c>
       <c r="P4">
-        <v>0.5876032848</v>
+        <v>0.5811049272000001</v>
       </c>
       <c r="Q4">
-        <v>0.9626032848</v>
+        <v>0.9561049272000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08474120870721982</v>
+        <v>0.08507951412283912</v>
       </c>
       <c r="T4">
-        <v>0.5360403955198746</v>
+        <v>0.5406972969057184</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>46.21167662425965</v>
+        <v>30.8077844161731</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08379468869915395</v>
+        <v>0.08369795286523246</v>
       </c>
       <c r="C5">
-        <v>15.2445240105278</v>
+        <v>15.10679349940171</v>
       </c>
       <c r="D5">
-        <v>12.7659240105278</v>
+        <v>12.78199349940171</v>
       </c>
       <c r="E5">
-        <v>-1.3186</v>
+        <v>-1.1648</v>
       </c>
       <c r="F5">
-        <v>0.4614</v>
+        <v>0.6152</v>
       </c>
       <c r="G5">
         <v>2.94</v>
@@ -1685,28 +1685,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M5">
-        <v>0.02320842</v>
+        <v>0.03094456</v>
       </c>
       <c r="N5">
-        <v>0.6917915800000001</v>
+        <v>0.6840554400000001</v>
       </c>
       <c r="O5">
-        <v>0.1106866528</v>
+        <v>0.1094488704</v>
       </c>
       <c r="P5">
-        <v>0.5811049272000001</v>
+        <v>0.5746065696</v>
       </c>
       <c r="Q5">
-        <v>0.9561049272000001</v>
+        <v>0.9496065696</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08507951412283912</v>
+        <v>0.08542486756795049</v>
       </c>
       <c r="T5">
-        <v>0.5406972969057184</v>
+        <v>0.5454512170704341</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>30.8077844161731</v>
+        <v>23.10583831212983</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08369795286523246</v>
+        <v>0.08360121703131101</v>
       </c>
       <c r="C6">
-        <v>15.10679349940171</v>
+        <v>14.96910349516489</v>
       </c>
       <c r="D6">
-        <v>12.78199349940171</v>
+        <v>12.79810349516489</v>
       </c>
       <c r="E6">
-        <v>-1.1648</v>
+        <v>-1.011</v>
       </c>
       <c r="F6">
-        <v>0.6152</v>
+        <v>0.769</v>
       </c>
       <c r="G6">
         <v>2.94</v>
@@ -1767,28 +1767,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M6">
-        <v>0.03094456</v>
+        <v>0.0386807</v>
       </c>
       <c r="N6">
-        <v>0.6840554400000001</v>
+        <v>0.6763193000000001</v>
       </c>
       <c r="O6">
-        <v>0.1094488704</v>
+        <v>0.108211088</v>
       </c>
       <c r="P6">
-        <v>0.5746065696</v>
+        <v>0.5681082120000001</v>
       </c>
       <c r="Q6">
-        <v>0.9496065696</v>
+        <v>0.9431082120000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08542486756795049</v>
+        <v>0.08577749161190633</v>
       </c>
       <c r="T6">
-        <v>0.5454512170704341</v>
+        <v>0.5503052197649333</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.10583831212983</v>
+        <v>18.48467064970386</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08360121703131101</v>
+        <v>0.08350448119738955</v>
       </c>
       <c r="C7">
-        <v>14.96910349516489</v>
+        <v>14.8314541511712</v>
       </c>
       <c r="D7">
-        <v>12.79810349516489</v>
+        <v>12.8142541511712</v>
       </c>
       <c r="E7">
-        <v>-1.011</v>
+        <v>-0.8572</v>
       </c>
       <c r="F7">
-        <v>0.769</v>
+        <v>0.9228000000000001</v>
       </c>
       <c r="G7">
         <v>2.94</v>
@@ -1849,28 +1849,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M7">
-        <v>0.0386807</v>
+        <v>0.04641684</v>
       </c>
       <c r="N7">
-        <v>0.6763193000000001</v>
+        <v>0.6685831600000001</v>
       </c>
       <c r="O7">
-        <v>0.108211088</v>
+        <v>0.1069733056</v>
       </c>
       <c r="P7">
-        <v>0.5681082120000001</v>
+        <v>0.5616098544000001</v>
       </c>
       <c r="Q7">
-        <v>0.9431082120000001</v>
+        <v>0.9366098544000001</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08577749161190633</v>
+        <v>0.08613761829509527</v>
       </c>
       <c r="T7">
-        <v>0.5503052197649333</v>
+        <v>0.555262499112507</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.48467064970386</v>
+        <v>15.40389220808655</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08350448119738955</v>
+        <v>0.08340774536346808</v>
       </c>
       <c r="C8">
-        <v>14.8314541511712</v>
+        <v>14.69384562154958</v>
       </c>
       <c r="D8">
-        <v>12.8142541511712</v>
+        <v>12.83044562154958</v>
       </c>
       <c r="E8">
-        <v>-0.8572000000000001</v>
+        <v>-0.7034000000000002</v>
       </c>
       <c r="F8">
-        <v>0.9228</v>
+        <v>1.0766</v>
       </c>
       <c r="G8">
         <v>2.94</v>
@@ -1931,28 +1931,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M8">
-        <v>0.04641683999999999</v>
+        <v>0.05415297999999999</v>
       </c>
       <c r="N8">
-        <v>0.6685831600000001</v>
+        <v>0.6608470200000001</v>
       </c>
       <c r="O8">
-        <v>0.1069733056</v>
+        <v>0.1057355232</v>
       </c>
       <c r="P8">
-        <v>0.5616098544000001</v>
+        <v>0.5551114968</v>
       </c>
       <c r="Q8">
-        <v>0.9366098544000001</v>
+        <v>0.9301114968</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08613761829509527</v>
+        <v>0.08650548963813771</v>
       </c>
       <c r="T8">
-        <v>0.555262499112507</v>
+        <v>0.5603263866180929</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.40389220808655</v>
+        <v>13.2033361783599</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08340774536346807</v>
+        <v>0.08341180952954662</v>
       </c>
       <c r="C9">
-        <v>14.69384562154957</v>
+        <v>14.53936454534162</v>
       </c>
       <c r="D9">
-        <v>12.83044562154958</v>
+        <v>12.82976454534162</v>
       </c>
       <c r="E9">
-        <v>-0.7034</v>
+        <v>-0.5496000000000001</v>
       </c>
       <c r="F9">
-        <v>1.0766</v>
+        <v>1.2304</v>
       </c>
       <c r="G9">
         <v>2.94</v>
@@ -2013,45 +2013,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M9">
-        <v>0.05415298</v>
+        <v>0.06373471999999999</v>
       </c>
       <c r="N9">
-        <v>0.6608470200000001</v>
+        <v>0.6512652800000001</v>
       </c>
       <c r="O9">
-        <v>0.1057355232</v>
+        <v>0.1042024448</v>
       </c>
       <c r="P9">
-        <v>0.5551114968</v>
+        <v>0.5470628352</v>
       </c>
       <c r="Q9">
-        <v>0.9301114968</v>
+        <v>0.9220628352</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08650548963813771</v>
+        <v>0.0868813581842898</v>
       </c>
       <c r="T9">
-        <v>0.5603263866180929</v>
+        <v>0.5655003586346699</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.16</v>
       </c>
       <c r="W9">
-        <v>0.042252</v>
+        <v>0.043512</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.2033361783599</v>
+        <v>11.21837516505917</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08341180952954662</v>
+        <v>0.08332767369562515</v>
       </c>
       <c r="C10">
-        <v>14.53936454534162</v>
+        <v>14.39967885777135</v>
       </c>
       <c r="D10">
-        <v>12.82976454534162</v>
+        <v>12.84387885777135</v>
       </c>
       <c r="E10">
-        <v>-0.5496000000000001</v>
+        <v>-0.3958000000000002</v>
       </c>
       <c r="F10">
-        <v>1.2304</v>
+        <v>1.3842</v>
       </c>
       <c r="G10">
         <v>2.94</v>
@@ -2095,28 +2095,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M10">
-        <v>0.06373471999999999</v>
+        <v>0.07170156</v>
       </c>
       <c r="N10">
-        <v>0.6512652800000001</v>
+        <v>0.6432984400000001</v>
       </c>
       <c r="O10">
-        <v>0.1042024448</v>
+        <v>0.1029277504</v>
       </c>
       <c r="P10">
-        <v>0.5470628352</v>
+        <v>0.5403706896000001</v>
       </c>
       <c r="Q10">
-        <v>0.9220628352</v>
+        <v>0.9153706896000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.0868813581842898</v>
+        <v>0.08726548757761005</v>
       </c>
       <c r="T10">
-        <v>0.5655003586346699</v>
+        <v>0.5707880443219407</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.21837516505917</v>
+        <v>9.971889035608154</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08332767369562515</v>
+        <v>0.08338633786170367</v>
       </c>
       <c r="C11">
-        <v>14.39967885777135</v>
+        <v>14.23603430176701</v>
       </c>
       <c r="D11">
-        <v>12.84387885777135</v>
+        <v>12.83403430176701</v>
       </c>
       <c r="E11">
-        <v>-0.3958000000000002</v>
+        <v>-0.2420000000000002</v>
       </c>
       <c r="F11">
-        <v>1.3842</v>
+        <v>1.538</v>
       </c>
       <c r="G11">
         <v>2.94</v>
@@ -2177,45 +2177,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M11">
-        <v>0.07170156</v>
+        <v>0.082283</v>
       </c>
       <c r="N11">
-        <v>0.6432984400000001</v>
+        <v>0.6327170000000001</v>
       </c>
       <c r="O11">
-        <v>0.1029277504</v>
+        <v>0.10123472</v>
       </c>
       <c r="P11">
-        <v>0.5403706896000001</v>
+        <v>0.5314822800000001</v>
       </c>
       <c r="Q11">
-        <v>0.9153706896000001</v>
+        <v>0.9064822800000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08726548757761005</v>
+        <v>0.08765815317967074</v>
       </c>
       <c r="T11">
-        <v>0.5707880443219407</v>
+        <v>0.5761932341355955</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.16</v>
       </c>
       <c r="W11">
-        <v>0.043512</v>
+        <v>0.04494</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>9.971889035608154</v>
+        <v>8.689522744673871</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08338633786170367</v>
+        <v>0.0833164820277822</v>
       </c>
       <c r="C12">
-        <v>14.23603430176701</v>
+        <v>14.09395867059461</v>
       </c>
       <c r="D12">
-        <v>12.83403430176701</v>
+        <v>12.84575867059461</v>
       </c>
       <c r="E12">
-        <v>-0.242</v>
+        <v>-0.08820000000000006</v>
       </c>
       <c r="F12">
-        <v>1.538</v>
+        <v>1.6918</v>
       </c>
       <c r="G12">
         <v>2.94</v>
@@ -2259,28 +2259,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M12">
-        <v>0.082283</v>
+        <v>0.0905113</v>
       </c>
       <c r="N12">
-        <v>0.6327170000000001</v>
+        <v>0.6244887000000001</v>
       </c>
       <c r="O12">
-        <v>0.10123472</v>
+        <v>0.09991819200000002</v>
       </c>
       <c r="P12">
-        <v>0.5314822800000001</v>
+        <v>0.524570508</v>
       </c>
       <c r="Q12">
-        <v>0.9064822800000001</v>
+        <v>0.899570508</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08765815317967074</v>
+        <v>0.08805964272784517</v>
       </c>
       <c r="T12">
-        <v>0.5761932341355955</v>
+        <v>0.5817198888888829</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.689522744673871</v>
+        <v>7.8995661315217</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0833164820277822</v>
+        <v>0.08332726619386072</v>
       </c>
       <c r="C13">
-        <v>14.09395867059461</v>
+        <v>13.93834729431145</v>
       </c>
       <c r="D13">
-        <v>12.84575867059461</v>
+        <v>12.84394729431145</v>
       </c>
       <c r="E13">
-        <v>-0.08820000000000006</v>
+        <v>0.06559999999999988</v>
       </c>
       <c r="F13">
-        <v>1.6918</v>
+        <v>1.8456</v>
       </c>
       <c r="G13">
         <v>2.94</v>
@@ -2341,45 +2341,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M13">
-        <v>0.0905113</v>
+        <v>0.10021608</v>
       </c>
       <c r="N13">
-        <v>0.6244887000000001</v>
+        <v>0.61478392</v>
       </c>
       <c r="O13">
-        <v>0.09991819200000002</v>
+        <v>0.09836542720000001</v>
       </c>
       <c r="P13">
-        <v>0.524570508</v>
+        <v>0.5164184928000001</v>
       </c>
       <c r="Q13">
-        <v>0.899570508</v>
+        <v>0.8914184928000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08805964272784517</v>
+        <v>0.08847025703847809</v>
       </c>
       <c r="T13">
-        <v>0.5817198888888829</v>
+        <v>0.5873721494320178</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.16</v>
       </c>
       <c r="W13">
-        <v>0.04494</v>
+        <v>0.045612</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>7.8995661315217</v>
+        <v>7.134583591774893</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08332726619386072</v>
+        <v>0.08326413035993926</v>
       </c>
       <c r="C14">
-        <v>13.93834729431145</v>
+        <v>13.79515925084428</v>
       </c>
       <c r="D14">
-        <v>12.84394729431145</v>
+        <v>12.85455925084428</v>
       </c>
       <c r="E14">
-        <v>0.06559999999999988</v>
+        <v>0.2193999999999998</v>
       </c>
       <c r="F14">
-        <v>1.8456</v>
+        <v>1.9994</v>
       </c>
       <c r="G14">
         <v>2.94</v>
@@ -2423,28 +2423,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M14">
-        <v>0.10021608</v>
+        <v>0.10856742</v>
       </c>
       <c r="N14">
-        <v>0.61478392</v>
+        <v>0.6064325800000001</v>
       </c>
       <c r="O14">
-        <v>0.09836542720000001</v>
+        <v>0.09702921280000001</v>
       </c>
       <c r="P14">
-        <v>0.5164184928000001</v>
+        <v>0.5094033672000001</v>
       </c>
       <c r="Q14">
-        <v>0.8914184928000001</v>
+        <v>0.8844033672000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08847025703847809</v>
+        <v>0.08889031075855088</v>
       </c>
       <c r="T14">
-        <v>0.5873721494320178</v>
+        <v>0.5931543469991328</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.134583591774893</v>
+        <v>6.585769469330671</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08326413035993926</v>
+        <v>0.08320099452601779</v>
       </c>
       <c r="C15">
-        <v>13.79515925084428</v>
+        <v>13.65198875754914</v>
       </c>
       <c r="D15">
-        <v>12.85455925084428</v>
+        <v>12.86518875754914</v>
       </c>
       <c r="E15">
-        <v>0.2193999999999998</v>
+        <v>0.3732</v>
       </c>
       <c r="F15">
-        <v>1.9994</v>
+        <v>2.1532</v>
       </c>
       <c r="G15">
         <v>2.94</v>
@@ -2505,28 +2505,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M15">
-        <v>0.10856742</v>
+        <v>0.11691876</v>
       </c>
       <c r="N15">
-        <v>0.6064325800000001</v>
+        <v>0.5980812400000001</v>
       </c>
       <c r="O15">
-        <v>0.09702921280000001</v>
+        <v>0.09569299840000001</v>
       </c>
       <c r="P15">
-        <v>0.5094033672000001</v>
+        <v>0.5023882416000001</v>
       </c>
       <c r="Q15">
-        <v>0.8844033672000001</v>
+        <v>0.8773882416000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08889031075855088</v>
+        <v>0.08932013316978812</v>
       </c>
       <c r="T15">
-        <v>0.5931543469991328</v>
+        <v>0.599071014277111</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.585769469330671</v>
+        <v>6.115357364378481</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08320099452601779</v>
+        <v>0.08326385869209631</v>
       </c>
       <c r="C16">
-        <v>13.65198875754914</v>
+        <v>13.48760495103319</v>
       </c>
       <c r="D16">
-        <v>12.86518875754914</v>
+        <v>12.85460495103319</v>
       </c>
       <c r="E16">
-        <v>0.3732</v>
+        <v>0.5270000000000004</v>
       </c>
       <c r="F16">
-        <v>2.1532</v>
+        <v>2.307</v>
       </c>
       <c r="G16">
         <v>2.94</v>
@@ -2587,45 +2587,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M16">
-        <v>0.11691876</v>
+        <v>0.1275771</v>
       </c>
       <c r="N16">
-        <v>0.5980812400000001</v>
+        <v>0.5874229000000001</v>
       </c>
       <c r="O16">
-        <v>0.09569299840000001</v>
+        <v>0.09398766400000001</v>
       </c>
       <c r="P16">
-        <v>0.5023882416000001</v>
+        <v>0.4934352360000001</v>
       </c>
       <c r="Q16">
-        <v>0.8773882416000001</v>
+        <v>0.8684352360000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08932013316978812</v>
+        <v>0.08976006904952508</v>
       </c>
       <c r="T16">
-        <v>0.599071014277111</v>
+        <v>0.6051268972557473</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.16</v>
       </c>
       <c r="W16">
-        <v>0.045612</v>
+        <v>0.046452</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.115357364378481</v>
+        <v>5.604454090898758</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08326385869209631</v>
+        <v>0.08320912285817486</v>
       </c>
       <c r="C17">
-        <v>13.48760495103319</v>
+        <v>13.34301929117978</v>
       </c>
       <c r="D17">
-        <v>12.85460495103319</v>
+        <v>12.86381929117978</v>
       </c>
       <c r="E17">
-        <v>0.5269999999999999</v>
+        <v>0.6807999999999998</v>
       </c>
       <c r="F17">
-        <v>2.307</v>
+        <v>2.4608</v>
       </c>
       <c r="G17">
         <v>2.94</v>
@@ -2669,28 +2669,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M17">
-        <v>0.1275771</v>
+        <v>0.13608224</v>
       </c>
       <c r="N17">
-        <v>0.5874229000000001</v>
+        <v>0.5789177600000001</v>
       </c>
       <c r="O17">
-        <v>0.09398766400000001</v>
+        <v>0.09262684160000001</v>
       </c>
       <c r="P17">
-        <v>0.4934352360000001</v>
+        <v>0.4862909184</v>
       </c>
       <c r="Q17">
-        <v>0.8684352360000001</v>
+        <v>0.8612909184</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08976006904952508</v>
+        <v>0.0902104795930653</v>
       </c>
       <c r="T17">
-        <v>0.6051268972557473</v>
+        <v>0.6113269679243513</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.604454090898759</v>
+        <v>5.254175710217587</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08320912285817486</v>
+        <v>0.08315438702425337</v>
       </c>
       <c r="C18">
-        <v>13.34301929117978</v>
+        <v>13.19844685070863</v>
       </c>
       <c r="D18">
-        <v>12.86381929117978</v>
+        <v>12.87304685070863</v>
       </c>
       <c r="E18">
-        <v>0.6807999999999998</v>
+        <v>0.8345999999999998</v>
       </c>
       <c r="F18">
-        <v>2.4608</v>
+        <v>2.6146</v>
       </c>
       <c r="G18">
         <v>2.94</v>
@@ -2751,28 +2751,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M18">
-        <v>0.13608224</v>
+        <v>0.14458738</v>
       </c>
       <c r="N18">
-        <v>0.5789177600000001</v>
+        <v>0.5704126200000001</v>
       </c>
       <c r="O18">
-        <v>0.09262684160000001</v>
+        <v>0.09126601920000002</v>
       </c>
       <c r="P18">
-        <v>0.4862909184</v>
+        <v>0.4791466008000002</v>
       </c>
       <c r="Q18">
-        <v>0.8612909184</v>
+        <v>0.8541466008000002</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0902104795930653</v>
+        <v>0.09067174340271492</v>
       </c>
       <c r="T18">
-        <v>0.6113269679243513</v>
+        <v>0.6176764378861748</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.254175710217587</v>
+        <v>4.945106550793024</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08315438702425337</v>
+        <v>0.0830996511903319</v>
       </c>
       <c r="C19">
-        <v>13.19844685070863</v>
+        <v>13.05388765808799</v>
       </c>
       <c r="D19">
-        <v>12.87304685070863</v>
+        <v>12.88228765808799</v>
       </c>
       <c r="E19">
-        <v>0.8345999999999998</v>
+        <v>0.9884000000000002</v>
       </c>
       <c r="F19">
-        <v>2.6146</v>
+        <v>2.7684</v>
       </c>
       <c r="G19">
         <v>2.94</v>
@@ -2833,28 +2833,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M19">
-        <v>0.14458738</v>
+        <v>0.15309252</v>
       </c>
       <c r="N19">
-        <v>0.5704126200000001</v>
+        <v>0.5619074800000001</v>
       </c>
       <c r="O19">
-        <v>0.09126601920000002</v>
+        <v>0.08990519680000002</v>
       </c>
       <c r="P19">
-        <v>0.4791466008000002</v>
+        <v>0.4720022832000001</v>
       </c>
       <c r="Q19">
-        <v>0.8541466008000002</v>
+        <v>0.8470022832000002</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09067174340271492</v>
+        <v>0.09114425754918526</v>
       </c>
       <c r="T19">
-        <v>0.6176764378861748</v>
+        <v>0.6241807729690181</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.945106550793024</v>
+        <v>4.6703784090823</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08309965119033191</v>
+        <v>0.08344391535641045</v>
       </c>
       <c r="C20">
-        <v>13.05388765808799</v>
+        <v>12.84218676587125</v>
       </c>
       <c r="D20">
-        <v>12.88228765808799</v>
+        <v>12.82438676587125</v>
       </c>
       <c r="E20">
-        <v>0.9883999999999997</v>
+        <v>1.1422</v>
       </c>
       <c r="F20">
-        <v>2.7684</v>
+        <v>2.9222</v>
       </c>
       <c r="G20">
         <v>2.94</v>
@@ -2915,45 +2915,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M20">
-        <v>0.15309252</v>
+        <v>0.16890316</v>
       </c>
       <c r="N20">
-        <v>0.5619074800000001</v>
+        <v>0.5460968400000001</v>
       </c>
       <c r="O20">
-        <v>0.08990519680000002</v>
+        <v>0.08737549440000002</v>
       </c>
       <c r="P20">
-        <v>0.4720022832000001</v>
+        <v>0.4587213456000001</v>
       </c>
       <c r="Q20">
-        <v>0.8470022832000002</v>
+        <v>0.8337213456000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09114425754918526</v>
+        <v>0.09162843871161783</v>
       </c>
       <c r="T20">
-        <v>0.6241807729690181</v>
+        <v>0.6308457089181045</v>
       </c>
       <c r="U20">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V20">
         <v>0.16</v>
       </c>
       <c r="W20">
-        <v>0.046452</v>
+        <v>0.048552</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.6703784090823</v>
+        <v>4.23319492660765</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08344391535641045</v>
+        <v>0.08341017952248897</v>
       </c>
       <c r="C21">
-        <v>12.84218676587125</v>
+        <v>12.69403769454573</v>
       </c>
       <c r="D21">
-        <v>12.82438676587125</v>
+        <v>12.83003769454573</v>
       </c>
       <c r="E21">
-        <v>1.1422</v>
+        <v>1.296</v>
       </c>
       <c r="F21">
-        <v>2.9222</v>
+        <v>3.076</v>
       </c>
       <c r="G21">
         <v>2.94</v>
@@ -2997,28 +2997,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M21">
-        <v>0.16890316</v>
+        <v>0.1777928</v>
       </c>
       <c r="N21">
-        <v>0.5460968400000001</v>
+        <v>0.5372072000000001</v>
       </c>
       <c r="O21">
-        <v>0.08737549440000002</v>
+        <v>0.08595315200000002</v>
       </c>
       <c r="P21">
-        <v>0.4587213456000001</v>
+        <v>0.4512540480000001</v>
       </c>
       <c r="Q21">
-        <v>0.8337213456000001</v>
+        <v>0.826254048</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09162843871161783</v>
+        <v>0.09212472440311122</v>
       </c>
       <c r="T21">
-        <v>0.6308457089181045</v>
+        <v>0.6376772682659182</v>
       </c>
       <c r="U21">
         <v>0.0578</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>4.23319492660765</v>
+        <v>4.021535180277267</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08341017952248897</v>
+        <v>0.08399384368856751</v>
       </c>
       <c r="C22">
-        <v>12.69403769454573</v>
+        <v>12.44316782614591</v>
       </c>
       <c r="D22">
-        <v>12.83003769454573</v>
+        <v>12.73296782614591</v>
       </c>
       <c r="E22">
-        <v>1.296</v>
+        <v>1.4498</v>
       </c>
       <c r="F22">
-        <v>3.076</v>
+        <v>3.2298</v>
       </c>
       <c r="G22">
         <v>2.94</v>
@@ -3079,45 +3079,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M22">
-        <v>0.1777928</v>
+        <v>0.19798674</v>
       </c>
       <c r="N22">
-        <v>0.5372072000000001</v>
+        <v>0.5170132600000001</v>
       </c>
       <c r="O22">
-        <v>0.08595315200000002</v>
+        <v>0.08272212160000002</v>
       </c>
       <c r="P22">
-        <v>0.4512540480000001</v>
+        <v>0.4342911384000001</v>
       </c>
       <c r="Q22">
-        <v>0.826254048</v>
+        <v>0.8092911384000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09212472440311122</v>
+        <v>0.09263357428932595</v>
       </c>
       <c r="T22">
-        <v>0.6376772682659182</v>
+        <v>0.6446817784832968</v>
       </c>
       <c r="U22">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V22">
         <v>0.16</v>
       </c>
       <c r="W22">
-        <v>0.048552</v>
+        <v>0.051492</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.021535180277267</v>
+        <v>3.611352962324649</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08399384368856751</v>
+        <v>0.08450694785464603</v>
       </c>
       <c r="C23">
-        <v>12.44316782614591</v>
+        <v>12.20523806589274</v>
       </c>
       <c r="D23">
-        <v>12.73296782614591</v>
+        <v>12.64883806589274</v>
       </c>
       <c r="E23">
-        <v>1.4498</v>
+        <v>1.6036</v>
       </c>
       <c r="F23">
-        <v>3.2298</v>
+        <v>3.3836</v>
       </c>
       <c r="G23">
         <v>2.94</v>
@@ -3161,45 +3161,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M23">
-        <v>0.19798674</v>
+        <v>0.21688876</v>
       </c>
       <c r="N23">
-        <v>0.5170132600000001</v>
+        <v>0.4981112400000001</v>
       </c>
       <c r="O23">
-        <v>0.08272212160000002</v>
+        <v>0.07969779840000001</v>
       </c>
       <c r="P23">
-        <v>0.4342911384000001</v>
+        <v>0.4184134416</v>
       </c>
       <c r="Q23">
-        <v>0.8092911384000001</v>
+        <v>0.7934134416</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09263357428932595</v>
+        <v>0.09315547160852056</v>
       </c>
       <c r="T23">
-        <v>0.6446817784832968</v>
+        <v>0.6518658915267619</v>
       </c>
       <c r="U23">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V23">
         <v>0.16</v>
       </c>
       <c r="W23">
-        <v>0.051492</v>
+        <v>0.053844</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y23">
-        <v>3.61135296232465</v>
+        <v>3.296620811516466</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08450694785464603</v>
+        <v>0.08452613202072456</v>
       </c>
       <c r="C24">
-        <v>12.20523806589274</v>
+        <v>12.04831413977224</v>
       </c>
       <c r="D24">
-        <v>12.64883806589274</v>
+        <v>12.64571413977224</v>
       </c>
       <c r="E24">
-        <v>1.6036</v>
+        <v>1.7574</v>
       </c>
       <c r="F24">
-        <v>3.3836</v>
+        <v>3.5374</v>
       </c>
       <c r="G24">
         <v>2.94</v>
@@ -3243,28 +3243,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M24">
-        <v>0.21688876</v>
+        <v>0.22674734</v>
       </c>
       <c r="N24">
-        <v>0.4981112400000001</v>
+        <v>0.4882526600000001</v>
       </c>
       <c r="O24">
-        <v>0.07969779840000001</v>
+        <v>0.07812042560000002</v>
       </c>
       <c r="P24">
-        <v>0.4184134416</v>
+        <v>0.4101322344</v>
       </c>
       <c r="Q24">
-        <v>0.7934134416</v>
+        <v>0.7851322344</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09315547160852056</v>
+        <v>0.09369092470223969</v>
       </c>
       <c r="T24">
-        <v>0.6518658915267619</v>
+        <v>0.6592366049090184</v>
       </c>
       <c r="U24">
         <v>0.0641</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.296620811516466</v>
+        <v>3.153289471885315</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08452613202072456</v>
+        <v>0.0845453161868031</v>
       </c>
       <c r="C25">
-        <v>12.04831413977224</v>
+        <v>11.89139175632384</v>
       </c>
       <c r="D25">
-        <v>12.64571413977224</v>
+        <v>12.64259175632385</v>
       </c>
       <c r="E25">
-        <v>1.7574</v>
+        <v>1.9112</v>
       </c>
       <c r="F25">
-        <v>3.5374</v>
+        <v>3.6912</v>
       </c>
       <c r="G25">
         <v>2.94</v>
@@ -3325,28 +3325,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M25">
-        <v>0.22674734</v>
+        <v>0.23660592</v>
       </c>
       <c r="N25">
-        <v>0.4882526600000001</v>
+        <v>0.4783940800000001</v>
       </c>
       <c r="O25">
-        <v>0.07812042560000002</v>
+        <v>0.07654305280000001</v>
       </c>
       <c r="P25">
-        <v>0.4101322344</v>
+        <v>0.4018510272</v>
       </c>
       <c r="Q25">
-        <v>0.7851322344</v>
+        <v>0.7768510272</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09369092470223969</v>
+        <v>0.09424046866684618</v>
       </c>
       <c r="T25">
-        <v>0.6592366049090184</v>
+        <v>0.6668012844329132</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.153289471885315</v>
+        <v>3.02190241055676</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.0845453161868031</v>
+        <v>0.08620250035288163</v>
       </c>
       <c r="C26">
-        <v>11.89139175632384</v>
+        <v>11.47356911508932</v>
       </c>
       <c r="D26">
-        <v>12.64259175632385</v>
+        <v>12.37856911508931</v>
       </c>
       <c r="E26">
-        <v>1.9112</v>
+        <v>2.065</v>
       </c>
       <c r="F26">
-        <v>3.6912</v>
+        <v>3.845</v>
       </c>
       <c r="G26">
         <v>2.94</v>
@@ -3407,45 +3407,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M26">
-        <v>0.23660592</v>
+        <v>0.2764555</v>
       </c>
       <c r="N26">
-        <v>0.4783940800000001</v>
+        <v>0.4385445000000001</v>
       </c>
       <c r="O26">
-        <v>0.07654305280000001</v>
+        <v>0.07016712000000001</v>
       </c>
       <c r="P26">
-        <v>0.4018510272</v>
+        <v>0.36837738</v>
       </c>
       <c r="Q26">
-        <v>0.7768510272</v>
+        <v>0.7433773800000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09424046866684618</v>
+        <v>0.0948046671371755</v>
       </c>
       <c r="T26">
-        <v>0.6668012844329132</v>
+        <v>0.6745676887441119</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.16</v>
       </c>
       <c r="W26">
-        <v>0.053844</v>
+        <v>0.06039600000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.02190241055676</v>
+        <v>2.586311359332695</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08620250035288163</v>
+        <v>0.08713896451896017</v>
       </c>
       <c r="C27">
-        <v>11.47356911508932</v>
+        <v>11.1753912186831</v>
       </c>
       <c r="D27">
-        <v>12.37856911508931</v>
+        <v>12.2341912186831</v>
       </c>
       <c r="E27">
-        <v>2.065</v>
+        <v>2.2188</v>
       </c>
       <c r="F27">
-        <v>3.845</v>
+        <v>3.9988</v>
       </c>
       <c r="G27">
         <v>2.94</v>
@@ -3489,45 +3489,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M27">
-        <v>0.2764555</v>
+        <v>0.30310904</v>
       </c>
       <c r="N27">
-        <v>0.4385445000000001</v>
+        <v>0.4118909600000001</v>
       </c>
       <c r="O27">
-        <v>0.07016712000000001</v>
+        <v>0.06590255360000001</v>
       </c>
       <c r="P27">
-        <v>0.36837738</v>
+        <v>0.3459884064000001</v>
       </c>
       <c r="Q27">
-        <v>0.7433773800000001</v>
+        <v>0.7209884064000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0948046671371755</v>
+        <v>0.09538411421481102</v>
       </c>
       <c r="T27">
-        <v>0.6745676887441119</v>
+        <v>0.6825439958745321</v>
       </c>
       <c r="U27">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V27">
         <v>0.16</v>
       </c>
       <c r="W27">
-        <v>0.06039600000000001</v>
+        <v>0.06367200000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y27">
-        <v>2.586311359332695</v>
+        <v>2.358887085650761</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08713896451896017</v>
+        <v>0.08725642868503869</v>
       </c>
       <c r="C28">
-        <v>11.1753912186831</v>
+        <v>11.00371873721171</v>
       </c>
       <c r="D28">
-        <v>12.2341912186831</v>
+        <v>12.21631873721171</v>
       </c>
       <c r="E28">
-        <v>2.2188</v>
+        <v>2.372599999999999</v>
       </c>
       <c r="F28">
-        <v>3.9988</v>
+        <v>4.1526</v>
       </c>
       <c r="G28">
         <v>2.94</v>
@@ -3571,28 +3571,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M28">
-        <v>0.30310904</v>
+        <v>0.31476708</v>
       </c>
       <c r="N28">
-        <v>0.4118909600000001</v>
+        <v>0.4002329200000001</v>
       </c>
       <c r="O28">
-        <v>0.06590255360000001</v>
+        <v>0.06403726720000001</v>
       </c>
       <c r="P28">
-        <v>0.3459884064000001</v>
+        <v>0.3361956528000001</v>
       </c>
       <c r="Q28">
-        <v>0.7209884064000001</v>
+        <v>0.7111956528000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09538411421481102</v>
+        <v>0.09597943655484752</v>
       </c>
       <c r="T28">
-        <v>0.6825439958745321</v>
+        <v>0.6907388319674296</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.358887085650761</v>
+        <v>2.271520897293326</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08725642868503869</v>
+        <v>0.08737389285111721</v>
       </c>
       <c r="C29">
-        <v>11.00371873721171</v>
+        <v>10.83209839807352</v>
       </c>
       <c r="D29">
-        <v>12.21631873721171</v>
+        <v>12.19849839807352</v>
       </c>
       <c r="E29">
-        <v>2.372599999999999</v>
+        <v>2.5264</v>
       </c>
       <c r="F29">
-        <v>4.1526</v>
+        <v>4.3064</v>
       </c>
       <c r="G29">
         <v>2.94</v>
@@ -3653,28 +3653,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M29">
-        <v>0.31476708</v>
+        <v>0.32642512</v>
       </c>
       <c r="N29">
-        <v>0.4002329200000001</v>
+        <v>0.3885748800000001</v>
       </c>
       <c r="O29">
-        <v>0.06403726720000001</v>
+        <v>0.06217198080000001</v>
       </c>
       <c r="P29">
-        <v>0.3361956528000001</v>
+        <v>0.3264028992</v>
       </c>
       <c r="Q29">
-        <v>0.7111956528000001</v>
+        <v>0.7014028992000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09597943655484752</v>
+        <v>0.09659129562655169</v>
       </c>
       <c r="T29">
-        <v>0.6907388319674296</v>
+        <v>0.6991613023962409</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.271520897293326</v>
+        <v>2.190395150961421</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08737389285111721</v>
+        <v>0.08749135701719575</v>
       </c>
       <c r="C30">
-        <v>10.83209839807352</v>
+        <v>10.66052997341578</v>
       </c>
       <c r="D30">
-        <v>12.19849839807352</v>
+        <v>12.18072997341578</v>
       </c>
       <c r="E30">
-        <v>2.5264</v>
+        <v>2.6802</v>
       </c>
       <c r="F30">
-        <v>4.3064</v>
+        <v>4.4602</v>
       </c>
       <c r="G30">
         <v>2.94</v>
@@ -3735,28 +3735,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M30">
-        <v>0.32642512</v>
+        <v>0.33808316</v>
       </c>
       <c r="N30">
-        <v>0.3885748800000001</v>
+        <v>0.37691684</v>
       </c>
       <c r="O30">
-        <v>0.06217198080000001</v>
+        <v>0.06030669440000001</v>
       </c>
       <c r="P30">
-        <v>0.3264028992</v>
+        <v>0.3166101456</v>
       </c>
       <c r="Q30">
-        <v>0.7014028992000001</v>
+        <v>0.6916101456</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09659129562655169</v>
+        <v>0.09722039016506444</v>
       </c>
       <c r="T30">
-        <v>0.6991613023962409</v>
+        <v>0.7078210255131878</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.190395150961421</v>
+        <v>2.114864283686889</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08749135701719574</v>
+        <v>0.08760882118327426</v>
       </c>
       <c r="C31">
-        <v>10.66052997341578</v>
+        <v>10.4890132367114</v>
       </c>
       <c r="D31">
-        <v>12.18072997341578</v>
+        <v>12.1630132367114</v>
       </c>
       <c r="E31">
-        <v>2.680199999999999</v>
+        <v>2.834</v>
       </c>
       <c r="F31">
-        <v>4.460199999999999</v>
+        <v>4.614</v>
       </c>
       <c r="G31">
         <v>2.94</v>
@@ -3817,28 +3817,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M31">
-        <v>0.33808316</v>
+        <v>0.3497412</v>
       </c>
       <c r="N31">
-        <v>0.3769168400000001</v>
+        <v>0.3652588000000001</v>
       </c>
       <c r="O31">
-        <v>0.06030669440000001</v>
+        <v>0.05844140800000001</v>
       </c>
       <c r="P31">
-        <v>0.3166101456000001</v>
+        <v>0.306817392</v>
       </c>
       <c r="Q31">
-        <v>0.6916101456000001</v>
+        <v>0.681817392</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09722039016506442</v>
+        <v>0.09786745883324896</v>
       </c>
       <c r="T31">
-        <v>0.7078210255131877</v>
+        <v>0.7167281692906188</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.11486428368689</v>
+        <v>2.044368807563993</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08760882118327426</v>
+        <v>0.09142396534935279</v>
       </c>
       <c r="C32">
-        <v>10.4890132367114</v>
+        <v>9.786543947259222</v>
       </c>
       <c r="D32">
-        <v>12.1630132367114</v>
+        <v>11.61434394725922</v>
       </c>
       <c r="E32">
-        <v>2.834</v>
+        <v>2.987799999999999</v>
       </c>
       <c r="F32">
-        <v>4.614</v>
+        <v>4.767799999999999</v>
       </c>
       <c r="G32">
         <v>2.94</v>
@@ -3899,45 +3899,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M32">
-        <v>0.3497412</v>
+        <v>0.4291019999999999</v>
       </c>
       <c r="N32">
-        <v>0.3652588000000001</v>
+        <v>0.2858980000000002</v>
       </c>
       <c r="O32">
-        <v>0.05844140800000001</v>
+        <v>0.04574368000000002</v>
       </c>
       <c r="P32">
-        <v>0.306817392</v>
+        <v>0.2401543200000001</v>
       </c>
       <c r="Q32">
-        <v>0.681817392</v>
+        <v>0.6151543200000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09786745883324896</v>
+        <v>0.09853328311500406</v>
       </c>
       <c r="T32">
-        <v>0.7167281692906188</v>
+        <v>0.7258934911485551</v>
       </c>
       <c r="U32">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V32">
         <v>0.16</v>
       </c>
       <c r="W32">
-        <v>0.06367200000000001</v>
+        <v>0.0756</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.044368807563993</v>
+        <v>1.666270490466137</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09142396534935279</v>
+        <v>0.09166070951543134</v>
       </c>
       <c r="C33">
-        <v>9.786543947259222</v>
+        <v>9.600323537585652</v>
       </c>
       <c r="D33">
-        <v>11.61434394725922</v>
+        <v>11.58192353758565</v>
       </c>
       <c r="E33">
-        <v>2.987799999999999</v>
+        <v>3.1416</v>
       </c>
       <c r="F33">
-        <v>4.767799999999999</v>
+        <v>4.9216</v>
       </c>
       <c r="G33">
         <v>2.94</v>
@@ -3981,28 +3981,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M33">
-        <v>0.4291019999999999</v>
+        <v>0.4429439999999999</v>
       </c>
       <c r="N33">
-        <v>0.2858980000000002</v>
+        <v>0.2720560000000001</v>
       </c>
       <c r="O33">
-        <v>0.04574368000000002</v>
+        <v>0.04352896000000002</v>
       </c>
       <c r="P33">
-        <v>0.2401543200000001</v>
+        <v>0.2285270400000001</v>
       </c>
       <c r="Q33">
-        <v>0.6151543200000001</v>
+        <v>0.6035270400000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09853328311500406</v>
+        <v>0.09921869046386962</v>
       </c>
       <c r="T33">
-        <v>0.7258934911485551</v>
+        <v>0.7353283812964307</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.666270490466137</v>
+        <v>1.61419953763907</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09166070951543134</v>
+        <v>0.09189745368150987</v>
       </c>
       <c r="C34">
-        <v>9.600323537585652</v>
+        <v>9.414283621469126</v>
       </c>
       <c r="D34">
-        <v>11.58192353758565</v>
+        <v>11.54968362146913</v>
       </c>
       <c r="E34">
-        <v>3.1416</v>
+        <v>3.2954</v>
       </c>
       <c r="F34">
-        <v>4.9216</v>
+        <v>5.0754</v>
       </c>
       <c r="G34">
         <v>2.94</v>
@@ -4063,28 +4063,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M34">
-        <v>0.4429439999999999</v>
+        <v>0.456786</v>
       </c>
       <c r="N34">
-        <v>0.2720560000000001</v>
+        <v>0.2582140000000001</v>
       </c>
       <c r="O34">
-        <v>0.04352896000000002</v>
+        <v>0.04131424000000002</v>
       </c>
       <c r="P34">
-        <v>0.2285270400000001</v>
+        <v>0.2168997600000001</v>
       </c>
       <c r="Q34">
-        <v>0.6035270400000001</v>
+        <v>0.5918997600000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09921869046386962</v>
+        <v>0.09992455773359682</v>
       </c>
       <c r="T34">
-        <v>0.7353283812964307</v>
+        <v>0.7450449099561832</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.61419953763907</v>
+        <v>1.565284400134856</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09189745368150987</v>
+        <v>0.0921341978475884</v>
       </c>
       <c r="C35">
-        <v>9.414283621469126</v>
+        <v>9.228422695806</v>
       </c>
       <c r="D35">
-        <v>11.54968362146913</v>
+        <v>11.517622695806</v>
       </c>
       <c r="E35">
-        <v>3.2954</v>
+        <v>3.449199999999999</v>
       </c>
       <c r="F35">
-        <v>5.0754</v>
+        <v>5.2292</v>
       </c>
       <c r="G35">
         <v>2.94</v>
@@ -4145,28 +4145,28 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M35">
-        <v>0.456786</v>
+        <v>0.4706279999999999</v>
       </c>
       <c r="N35">
-        <v>0.2582140000000001</v>
+        <v>0.2443720000000001</v>
       </c>
       <c r="O35">
-        <v>0.04131424000000002</v>
+        <v>0.03909952000000003</v>
       </c>
       <c r="P35">
-        <v>0.2168997600000001</v>
+        <v>0.2052724800000001</v>
       </c>
       <c r="Q35">
-        <v>0.5918997600000001</v>
+        <v>0.5802724800000001</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09992455773359682</v>
+        <v>0.1006518149205885</v>
       </c>
       <c r="T35">
-        <v>0.7450449099561832</v>
+        <v>0.7550558788783525</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.565284400134856</v>
+        <v>1.519246623660301</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0921341978475884</v>
+        <v>0.1100568015180855</v>
       </c>
       <c r="C36">
-        <v>9.228422695806</v>
+        <v>7.074522711130068</v>
       </c>
       <c r="D36">
-        <v>11.517622695806</v>
+        <v>9.517522711130068</v>
       </c>
       <c r="E36">
-        <v>3.449199999999999</v>
+        <v>3.603</v>
       </c>
       <c r="F36">
-        <v>5.2292</v>
+        <v>5.383</v>
       </c>
       <c r="G36">
         <v>2.94</v>
@@ -4227,45 +4227,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M36">
-        <v>0.4706279999999999</v>
+        <v>0.7902244</v>
       </c>
       <c r="N36">
-        <v>0.2443720000000001</v>
+        <v>-0.07522439999999997</v>
       </c>
       <c r="O36">
-        <v>0.03909952000000003</v>
+        <v>-0.01203590399999999</v>
       </c>
       <c r="P36">
-        <v>0.2052724800000001</v>
+        <v>-0.06318849599999997</v>
       </c>
       <c r="Q36">
-        <v>0.5802724800000001</v>
+        <v>0.311811504</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1006518149205885</v>
+        <v>0.1017154353654252</v>
       </c>
       <c r="T36">
-        <v>0.7550558788783525</v>
+        <v>0.7696970146535644</v>
       </c>
       <c r="U36">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V36">
-        <v>0.16</v>
+        <v>0.1447690048548235</v>
       </c>
       <c r="W36">
-        <v>0.0756</v>
+        <v>0.1255479100873119</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.519246623660301</v>
+        <v>0.904806280342647</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1100568015180855</v>
+        <v>0.1110668015180855</v>
       </c>
       <c r="C37">
-        <v>7.074522711130068</v>
+        <v>6.828486029452059</v>
       </c>
       <c r="D37">
-        <v>9.517522711130068</v>
+        <v>9.42528602945206</v>
       </c>
       <c r="E37">
-        <v>3.603</v>
+        <v>3.7568</v>
       </c>
       <c r="F37">
-        <v>5.383</v>
+        <v>5.5368</v>
       </c>
       <c r="G37">
         <v>2.94</v>
@@ -4309,37 +4309,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M37">
-        <v>0.7902244</v>
+        <v>0.8128022400000001</v>
       </c>
       <c r="N37">
-        <v>-0.07522439999999997</v>
+        <v>-0.09780224000000004</v>
       </c>
       <c r="O37">
-        <v>-0.01203590399999999</v>
+        <v>-0.01564835840000001</v>
       </c>
       <c r="P37">
-        <v>-0.06318849599999997</v>
+        <v>-0.08215388160000003</v>
       </c>
       <c r="Q37">
-        <v>0.311811504</v>
+        <v>0.2928461184</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1017154353654252</v>
+        <v>0.1025891140430099</v>
       </c>
       <c r="T37">
-        <v>0.7696970146535644</v>
+        <v>0.7817235305075265</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.1447690048548235</v>
+        <v>0.1407476436088562</v>
       </c>
       <c r="W37">
-        <v>0.1255479100873119</v>
+        <v>0.1261382459182199</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.904806280342647</v>
+        <v>0.8796727725553511</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1110668015180855</v>
+        <v>0.1120768015180855</v>
       </c>
       <c r="C38">
-        <v>6.828486029452062</v>
+        <v>6.584219965559413</v>
       </c>
       <c r="D38">
-        <v>9.425286029452062</v>
+        <v>9.334819965559413</v>
       </c>
       <c r="E38">
-        <v>3.756799999999999</v>
+        <v>3.9106</v>
       </c>
       <c r="F38">
-        <v>5.536799999999999</v>
+        <v>5.6906</v>
       </c>
       <c r="G38">
         <v>2.94</v>
@@ -4391,37 +4391,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M38">
-        <v>0.81280224</v>
+        <v>0.8353800800000001</v>
       </c>
       <c r="N38">
-        <v>-0.09780223999999993</v>
+        <v>-0.12038008</v>
       </c>
       <c r="O38">
-        <v>-0.01564835839999999</v>
+        <v>-0.0192608128</v>
       </c>
       <c r="P38">
-        <v>-0.08215388159999994</v>
+        <v>-0.1011192672</v>
       </c>
       <c r="Q38">
-        <v>0.2928461184000001</v>
+        <v>0.2738807328</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1025891140430099</v>
+        <v>0.1034905285516291</v>
       </c>
       <c r="T38">
-        <v>0.7817235305075265</v>
+        <v>0.7941318405155824</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1407476436088562</v>
+        <v>0.1369436532410493</v>
       </c>
       <c r="W38">
-        <v>0.1261382459182199</v>
+        <v>0.126696671704214</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.8796727725553513</v>
+        <v>0.855897832756558</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1120768015180855</v>
+        <v>0.1130868015180855</v>
       </c>
       <c r="C39">
-        <v>6.584219965559413</v>
+        <v>6.341674019769033</v>
       </c>
       <c r="D39">
-        <v>9.334819965559413</v>
+        <v>9.246074019769033</v>
       </c>
       <c r="E39">
-        <v>3.9106</v>
+        <v>4.064399999999999</v>
       </c>
       <c r="F39">
-        <v>5.6906</v>
+        <v>5.844399999999999</v>
       </c>
       <c r="G39">
         <v>2.94</v>
@@ -4473,37 +4473,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M39">
-        <v>0.8353800800000001</v>
+        <v>0.85795792</v>
       </c>
       <c r="N39">
-        <v>-0.12038008</v>
+        <v>-0.14295792</v>
       </c>
       <c r="O39">
-        <v>-0.0192608128</v>
+        <v>-0.02287326719999999</v>
       </c>
       <c r="P39">
-        <v>-0.1011192672</v>
+        <v>-0.1200846528</v>
       </c>
       <c r="Q39">
-        <v>0.2738807328</v>
+        <v>0.2549153472</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1034905285516291</v>
+        <v>0.1044210209476231</v>
       </c>
       <c r="T39">
-        <v>0.7941318405155824</v>
+        <v>0.8069404185884144</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.1369436532410493</v>
+        <v>0.1333398728926006</v>
       </c>
       <c r="W39">
-        <v>0.126696671704214</v>
+        <v>0.1272257066593663</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.855897832756558</v>
+        <v>0.8333742055787539</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1130868015180855</v>
+        <v>0.1140968015180855</v>
       </c>
       <c r="C40">
-        <v>6.341674019769033</v>
+        <v>6.100799594710469</v>
       </c>
       <c r="D40">
-        <v>9.246074019769033</v>
+        <v>9.158999594710469</v>
       </c>
       <c r="E40">
-        <v>4.064399999999999</v>
+        <v>4.2182</v>
       </c>
       <c r="F40">
-        <v>5.844399999999999</v>
+        <v>5.9982</v>
       </c>
       <c r="G40">
         <v>2.94</v>
@@ -4555,37 +4555,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M40">
-        <v>0.85795792</v>
+        <v>0.88053576</v>
       </c>
       <c r="N40">
-        <v>-0.14295792</v>
+        <v>-0.1655357599999999</v>
       </c>
       <c r="O40">
-        <v>-0.02287326719999999</v>
+        <v>-0.02648572159999999</v>
       </c>
       <c r="P40">
-        <v>-0.1200846528</v>
+        <v>-0.1390500383999999</v>
       </c>
       <c r="Q40">
-        <v>0.2549153472</v>
+        <v>0.2359499616000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1044210209476231</v>
+        <v>0.1053820212910268</v>
       </c>
       <c r="T40">
-        <v>0.8069404185884144</v>
+        <v>0.8201689500406835</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1333398728926006</v>
+        <v>0.1299209017927904</v>
       </c>
       <c r="W40">
-        <v>0.1272257066593663</v>
+        <v>0.1277276116168184</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8333742055787539</v>
+        <v>0.8120056362049397</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1140968015180855</v>
+        <v>0.1372284778802527</v>
       </c>
       <c r="C41">
-        <v>6.100799594710469</v>
+        <v>4.322026647269964</v>
       </c>
       <c r="D41">
-        <v>9.158999594710469</v>
+        <v>7.534026647269965</v>
       </c>
       <c r="E41">
-        <v>4.2182</v>
+        <v>4.372</v>
       </c>
       <c r="F41">
-        <v>5.9982</v>
+        <v>6.152</v>
       </c>
       <c r="G41">
         <v>2.94</v>
@@ -4637,45 +4637,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M41">
-        <v>0.88053576</v>
+        <v>1.2353216</v>
       </c>
       <c r="N41">
-        <v>-0.1655357599999999</v>
+        <v>-0.5203215999999999</v>
       </c>
       <c r="O41">
-        <v>-0.02648572159999999</v>
+        <v>-0.08325145599999999</v>
       </c>
       <c r="P41">
-        <v>-0.1390500383999999</v>
+        <v>-0.4370701439999999</v>
       </c>
       <c r="Q41">
-        <v>0.2359499616000001</v>
+        <v>-0.06207014399999994</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1053820212910268</v>
+        <v>0.1072445155828225</v>
       </c>
       <c r="T41">
-        <v>0.8201689500406835</v>
+        <v>0.8458068850193836</v>
       </c>
       <c r="U41">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V41">
-        <v>0.1299209017927904</v>
+        <v>0.0926074635139546</v>
       </c>
       <c r="W41">
-        <v>0.1277276116168184</v>
+        <v>0.1822044213263979</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y41">
-        <v>0.8120056362049397</v>
+        <v>0.5787966469622162</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1372284778802527</v>
+        <v>0.1387784778802527</v>
       </c>
       <c r="C42">
-        <v>4.322026647269964</v>
+        <v>4.079711574789854</v>
       </c>
       <c r="D42">
-        <v>7.534026647269965</v>
+        <v>7.445511574789854</v>
       </c>
       <c r="E42">
-        <v>4.372</v>
+        <v>4.525799999999999</v>
       </c>
       <c r="F42">
-        <v>6.152</v>
+        <v>6.3058</v>
       </c>
       <c r="G42">
         <v>2.94</v>
@@ -4719,37 +4719,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M42">
-        <v>1.2353216</v>
+        <v>1.26620464</v>
       </c>
       <c r="N42">
-        <v>-0.5203215999999999</v>
+        <v>-0.5512046399999999</v>
       </c>
       <c r="O42">
-        <v>-0.08325145599999999</v>
+        <v>-0.08819274239999998</v>
       </c>
       <c r="P42">
-        <v>-0.4370701439999999</v>
+        <v>-0.4630118975999999</v>
       </c>
       <c r="Q42">
-        <v>-0.06207014399999994</v>
+        <v>-0.08801189759999994</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1072445155828225</v>
+        <v>0.108285948050328</v>
       </c>
       <c r="T42">
-        <v>0.8458068850193836</v>
+        <v>0.8601425949349664</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.0926074635139546</v>
+        <v>0.09034874489166303</v>
       </c>
       <c r="W42">
-        <v>0.1822044213263979</v>
+        <v>0.1826579720257541</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5787966469622162</v>
+        <v>0.5646796555728939</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1387784778802527</v>
+        <v>0.1403284778802527</v>
       </c>
       <c r="C43">
-        <v>4.079711574789854</v>
+        <v>3.839452225543337</v>
       </c>
       <c r="D43">
-        <v>7.445511574789854</v>
+        <v>7.359052225543336</v>
       </c>
       <c r="E43">
-        <v>4.525799999999999</v>
+        <v>4.6796</v>
       </c>
       <c r="F43">
-        <v>6.3058</v>
+        <v>6.4596</v>
       </c>
       <c r="G43">
         <v>2.94</v>
@@ -4801,37 +4801,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M43">
-        <v>1.26620464</v>
+        <v>1.29708768</v>
       </c>
       <c r="N43">
-        <v>-0.5512046399999999</v>
+        <v>-0.5820876799999999</v>
       </c>
       <c r="O43">
-        <v>-0.08819274239999998</v>
+        <v>-0.09313402879999998</v>
       </c>
       <c r="P43">
-        <v>-0.4630118975999999</v>
+        <v>-0.4889536511999999</v>
       </c>
       <c r="Q43">
-        <v>-0.08801189759999994</v>
+        <v>-0.1139536511999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.108285948050328</v>
+        <v>0.1093632919822302</v>
       </c>
       <c r="T43">
-        <v>0.8601425949349664</v>
+        <v>0.8749726396752244</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.09034874489166303</v>
+        <v>0.08819758429900437</v>
       </c>
       <c r="W43">
-        <v>0.1826579720257541</v>
+        <v>0.1830899250727599</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5646796555728939</v>
+        <v>0.5512349018687774</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1403284778802527</v>
+        <v>0.1418784778802527</v>
       </c>
       <c r="C44">
-        <v>3.839452225543337</v>
+        <v>3.601177806708136</v>
       </c>
       <c r="D44">
-        <v>7.359052225543336</v>
+        <v>7.274577806708135</v>
       </c>
       <c r="E44">
-        <v>4.679599999999999</v>
+        <v>4.833399999999999</v>
       </c>
       <c r="F44">
-        <v>6.459599999999999</v>
+        <v>6.6134</v>
       </c>
       <c r="G44">
         <v>2.94</v>
@@ -4883,37 +4883,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M44">
-        <v>1.29708768</v>
+        <v>1.32797072</v>
       </c>
       <c r="N44">
-        <v>-0.5820876799999999</v>
+        <v>-0.6129707199999999</v>
       </c>
       <c r="O44">
-        <v>-0.09313402879999998</v>
+        <v>-0.09807531519999999</v>
       </c>
       <c r="P44">
-        <v>-0.4889536511999999</v>
+        <v>-0.5148954047999998</v>
       </c>
       <c r="Q44">
-        <v>-0.1139536511999999</v>
+        <v>-0.1398954047999998</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1093632919822302</v>
+        <v>0.1104784374556027</v>
       </c>
       <c r="T44">
-        <v>0.8749726396752244</v>
+        <v>0.890323036862509</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.08819758429900437</v>
+        <v>0.08614647768739962</v>
       </c>
       <c r="W44">
-        <v>0.1830899250727599</v>
+        <v>0.1835017872803702</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5512349018687774</v>
+        <v>0.5384154855462477</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1418784778802527</v>
+        <v>0.1434284778802527</v>
       </c>
       <c r="C45">
-        <v>3.601177806708136</v>
+        <v>3.364820739090567</v>
       </c>
       <c r="D45">
-        <v>7.274577806708135</v>
+        <v>7.192020739090568</v>
       </c>
       <c r="E45">
-        <v>4.833399999999999</v>
+        <v>4.9872</v>
       </c>
       <c r="F45">
-        <v>6.6134</v>
+        <v>6.7672</v>
       </c>
       <c r="G45">
         <v>2.94</v>
@@ -4965,37 +4965,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M45">
-        <v>1.32797072</v>
+        <v>1.35885376</v>
       </c>
       <c r="N45">
-        <v>-0.6129707199999999</v>
+        <v>-0.6438537599999998</v>
       </c>
       <c r="O45">
-        <v>-0.09807531519999999</v>
+        <v>-0.1030166016</v>
       </c>
       <c r="P45">
-        <v>-0.5148954047999998</v>
+        <v>-0.5408371583999998</v>
       </c>
       <c r="Q45">
-        <v>-0.1398954047999998</v>
+        <v>-0.1658371583999998</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1104784374556027</v>
+        <v>0.1116334095530241</v>
       </c>
       <c r="T45">
-        <v>0.890323036862509</v>
+        <v>0.9062216625207682</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.08614647768739962</v>
+        <v>0.08418860319450419</v>
       </c>
       <c r="W45">
-        <v>0.1835017872803702</v>
+        <v>0.1838949284785436</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.5384154855462477</v>
+        <v>0.5261787699656512</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1434284778802527</v>
+        <v>0.1449784778802527</v>
       </c>
       <c r="C46">
-        <v>3.364820739090567</v>
+        <v>3.130316476819113</v>
       </c>
       <c r="D46">
-        <v>7.192020739090568</v>
+        <v>7.111316476819113</v>
       </c>
       <c r="E46">
-        <v>4.9872</v>
+        <v>5.140999999999999</v>
       </c>
       <c r="F46">
-        <v>6.7672</v>
+        <v>6.920999999999999</v>
       </c>
       <c r="G46">
         <v>2.94</v>
@@ -5047,37 +5047,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M46">
-        <v>1.35885376</v>
+        <v>1.3897368</v>
       </c>
       <c r="N46">
-        <v>-0.6438537599999998</v>
+        <v>-0.6747367999999998</v>
       </c>
       <c r="O46">
-        <v>-0.1030166016</v>
+        <v>-0.107957888</v>
       </c>
       <c r="P46">
-        <v>-0.5408371583999998</v>
+        <v>-0.5667789119999999</v>
       </c>
       <c r="Q46">
-        <v>-0.1658371583999998</v>
+        <v>-0.1917789119999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1116334095530241</v>
+        <v>0.1128303806358064</v>
       </c>
       <c r="T46">
-        <v>0.9062216625207682</v>
+        <v>0.9226984200211458</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.08418860319450419</v>
+        <v>0.08231774534573744</v>
       </c>
       <c r="W46">
-        <v>0.1838949284785436</v>
+        <v>0.1842705967345759</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5261787699656512</v>
+        <v>0.5144859084108588</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1449784778802527</v>
+        <v>0.1465284778802527</v>
       </c>
       <c r="C47">
-        <v>3.130316476819113</v>
+        <v>2.897603339042961</v>
       </c>
       <c r="D47">
-        <v>7.111316476819113</v>
+        <v>7.032403339042961</v>
       </c>
       <c r="E47">
-        <v>5.140999999999999</v>
+        <v>5.2948</v>
       </c>
       <c r="F47">
-        <v>6.920999999999999</v>
+        <v>7.0748</v>
       </c>
       <c r="G47">
         <v>2.94</v>
@@ -5129,37 +5129,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M47">
-        <v>1.3897368</v>
+        <v>1.42061984</v>
       </c>
       <c r="N47">
-        <v>-0.6747367999999998</v>
+        <v>-0.70561984</v>
       </c>
       <c r="O47">
-        <v>-0.107957888</v>
+        <v>-0.1128991744</v>
       </c>
       <c r="P47">
-        <v>-0.5667789119999999</v>
+        <v>-0.5927206656</v>
       </c>
       <c r="Q47">
-        <v>-0.1917789119999999</v>
+        <v>-0.2177206656</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1128303806358064</v>
+        <v>0.1140716839809139</v>
       </c>
       <c r="T47">
-        <v>0.9226984200211458</v>
+        <v>0.9397854277993151</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.08231774534573744</v>
+        <v>0.08052822914256921</v>
       </c>
       <c r="W47">
-        <v>0.1842705967345759</v>
+        <v>0.1846299315881721</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5144859084108588</v>
+        <v>0.5033014321410576</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1465284778802527</v>
+        <v>0.1647389805935388</v>
       </c>
       <c r="C48">
-        <v>2.897603339042961</v>
+        <v>1.932709091477282</v>
       </c>
       <c r="D48">
-        <v>7.032403339042961</v>
+        <v>6.221309091477282</v>
       </c>
       <c r="E48">
-        <v>5.2948</v>
+        <v>5.4486</v>
       </c>
       <c r="F48">
-        <v>7.0748</v>
+        <v>7.2286</v>
       </c>
       <c r="G48">
         <v>2.94</v>
@@ -5211,45 +5211,45 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M48">
-        <v>1.42061984</v>
+        <v>1.70450388</v>
       </c>
       <c r="N48">
-        <v>-0.70561984</v>
+        <v>-0.98950388</v>
       </c>
       <c r="O48">
-        <v>-0.1128991744</v>
+        <v>-0.1583206208</v>
       </c>
       <c r="P48">
-        <v>-0.5927206656</v>
+        <v>-0.8311832592</v>
       </c>
       <c r="Q48">
-        <v>-0.2177206656</v>
+        <v>-0.4561832592</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1140716839809139</v>
+        <v>0.1157570038924144</v>
       </c>
       <c r="T48">
-        <v>0.9397854277993151</v>
+        <v>0.9629844907439319</v>
       </c>
       <c r="U48">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.08052822914256921</v>
+        <v>0.06711630366015946</v>
       </c>
       <c r="W48">
-        <v>0.1846299315881721</v>
+        <v>0.2199739755969344</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y48">
-        <v>0.5033014321410576</v>
+        <v>0.4194768978759966</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1647389805935388</v>
+        <v>0.1666389805935388</v>
       </c>
       <c r="C49">
-        <v>1.932709091477282</v>
+        <v>1.704933913315708</v>
       </c>
       <c r="D49">
-        <v>6.221309091477282</v>
+        <v>6.147333913315709</v>
       </c>
       <c r="E49">
-        <v>5.4486</v>
+        <v>5.6024</v>
       </c>
       <c r="F49">
-        <v>7.2286</v>
+        <v>7.382400000000001</v>
       </c>
       <c r="G49">
         <v>2.94</v>
@@ -5293,37 +5293,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M49">
-        <v>1.70450388</v>
+        <v>1.74076992</v>
       </c>
       <c r="N49">
-        <v>-0.98950388</v>
+        <v>-1.02576992</v>
       </c>
       <c r="O49">
-        <v>-0.1583206208</v>
+        <v>-0.1641231872</v>
       </c>
       <c r="P49">
-        <v>-0.8311832592</v>
+        <v>-0.8616467328000001</v>
       </c>
       <c r="Q49">
-        <v>-0.4561832592</v>
+        <v>-0.4866467328000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1157570038924144</v>
+        <v>0.1171023308903455</v>
       </c>
       <c r="T49">
-        <v>0.9629844907439319</v>
+        <v>0.9815034232582383</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.06711630366015946</v>
+        <v>0.06571804733390614</v>
       </c>
       <c r="W49">
-        <v>0.2199739755969344</v>
+        <v>0.2203036844386649</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4194768978759966</v>
+        <v>0.4107377958369134</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1666389805935388</v>
+        <v>0.1685389805935388</v>
       </c>
       <c r="C50">
-        <v>1.704933913315711</v>
+        <v>1.478897283168699</v>
       </c>
       <c r="D50">
-        <v>6.14733391331571</v>
+        <v>6.075097283168698</v>
       </c>
       <c r="E50">
-        <v>5.602399999999999</v>
+        <v>5.756199999999999</v>
       </c>
       <c r="F50">
-        <v>7.3824</v>
+        <v>7.536199999999999</v>
       </c>
       <c r="G50">
         <v>2.94</v>
@@ -5375,37 +5375,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M50">
-        <v>1.74076992</v>
+        <v>1.77703596</v>
       </c>
       <c r="N50">
-        <v>-1.02576992</v>
+        <v>-1.06203596</v>
       </c>
       <c r="O50">
-        <v>-0.1641231872</v>
+        <v>-0.1699257536</v>
       </c>
       <c r="P50">
-        <v>-0.8616467327999999</v>
+        <v>-0.8921102063999998</v>
       </c>
       <c r="Q50">
-        <v>-0.4866467327999999</v>
+        <v>-0.5171102063999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1171023308903455</v>
+        <v>0.118500415809764</v>
       </c>
       <c r="T50">
-        <v>0.9815034232582383</v>
+        <v>1.000748588420164</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.06571804733390614</v>
+        <v>0.06437686269443868</v>
       </c>
       <c r="W50">
-        <v>0.2203036844386649</v>
+        <v>0.2206199357766514</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4107377958369134</v>
+        <v>0.4023553918402417</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1685389805935388</v>
+        <v>0.1704389805935388</v>
       </c>
       <c r="C51">
-        <v>1.478897283168699</v>
+        <v>1.254538624418112</v>
       </c>
       <c r="D51">
-        <v>6.075097283168698</v>
+        <v>6.004538624418112</v>
       </c>
       <c r="E51">
-        <v>5.756199999999999</v>
+        <v>5.909999999999999</v>
       </c>
       <c r="F51">
-        <v>7.536199999999999</v>
+        <v>7.69</v>
       </c>
       <c r="G51">
         <v>2.94</v>
@@ -5457,37 +5457,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M51">
-        <v>1.77703596</v>
+        <v>1.813302</v>
       </c>
       <c r="N51">
-        <v>-1.06203596</v>
+        <v>-1.098302</v>
       </c>
       <c r="O51">
-        <v>-0.1699257536</v>
+        <v>-0.17572832</v>
       </c>
       <c r="P51">
-        <v>-0.8921102063999998</v>
+        <v>-0.92257368</v>
       </c>
       <c r="Q51">
-        <v>-0.5171102063999998</v>
+        <v>-0.54757368</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.118500415809764</v>
+        <v>0.1199544241259593</v>
       </c>
       <c r="T51">
-        <v>1.000748588420164</v>
+        <v>1.020763560188568</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.06437686269443868</v>
+        <v>0.0630893254405499</v>
       </c>
       <c r="W51">
-        <v>0.2206199357766514</v>
+        <v>0.2209235370611183</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4023553918402417</v>
+        <v>0.3943082840034369</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1704389805935388</v>
+        <v>0.1723389805935388</v>
       </c>
       <c r="C52">
-        <v>1.254538624418112</v>
+        <v>1.031800142381528</v>
       </c>
       <c r="D52">
-        <v>6.004538624418112</v>
+        <v>5.935600142381528</v>
       </c>
       <c r="E52">
-        <v>5.909999999999999</v>
+        <v>6.0638</v>
       </c>
       <c r="F52">
-        <v>7.69</v>
+        <v>7.8438</v>
       </c>
       <c r="G52">
         <v>2.94</v>
@@ -5539,37 +5539,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M52">
-        <v>1.813302</v>
+        <v>1.84956804</v>
       </c>
       <c r="N52">
-        <v>-1.098302</v>
+        <v>-1.13456804</v>
       </c>
       <c r="O52">
-        <v>-0.17572832</v>
+        <v>-0.1815308864</v>
       </c>
       <c r="P52">
-        <v>-0.92257368</v>
+        <v>-0.9530371536</v>
       </c>
       <c r="Q52">
-        <v>-0.54757368</v>
+        <v>-0.5780371536</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1199544241259593</v>
+        <v>0.1214677797203667</v>
       </c>
       <c r="T52">
-        <v>1.020763560188568</v>
+        <v>1.041595469580171</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0630893254405499</v>
+        <v>0.06185227984367637</v>
       </c>
       <c r="W52">
-        <v>0.2209235370611183</v>
+        <v>0.2212152324128611</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3943082840034369</v>
+        <v>0.3865767490229773</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1723389805935388</v>
+        <v>0.1742389805935388</v>
       </c>
       <c r="C53">
-        <v>1.031800142381528</v>
+        <v>0.810626666427031</v>
       </c>
       <c r="D53">
-        <v>5.935600142381528</v>
+        <v>5.86822666642703</v>
       </c>
       <c r="E53">
-        <v>6.0638</v>
+        <v>6.217599999999999</v>
       </c>
       <c r="F53">
-        <v>7.8438</v>
+        <v>7.997599999999999</v>
       </c>
       <c r="G53">
         <v>2.94</v>
@@ -5621,37 +5621,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M53">
-        <v>1.84956804</v>
+        <v>1.88583408</v>
       </c>
       <c r="N53">
-        <v>-1.13456804</v>
+        <v>-1.17083408</v>
       </c>
       <c r="O53">
-        <v>-0.1815308864</v>
+        <v>-0.1873334528</v>
       </c>
       <c r="P53">
-        <v>-0.9530371536</v>
+        <v>-0.9835006271999999</v>
       </c>
       <c r="Q53">
-        <v>-0.5780371536</v>
+        <v>-0.6085006271999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1214677797203667</v>
+        <v>0.1230441917978743</v>
       </c>
       <c r="T53">
-        <v>1.041595469580171</v>
+        <v>1.063295375196425</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06185227984367637</v>
+        <v>0.06066281292360567</v>
       </c>
       <c r="W53">
-        <v>0.2212152324128611</v>
+        <v>0.2214957087126138</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3865767490229773</v>
+        <v>0.3791425807725355</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1742389805935388</v>
+        <v>0.1761389805935388</v>
       </c>
       <c r="C54">
-        <v>0.810626666427031</v>
+        <v>0.5909655027200262</v>
       </c>
       <c r="D54">
-        <v>5.86822666642703</v>
+        <v>5.802365502720026</v>
       </c>
       <c r="E54">
-        <v>6.217599999999999</v>
+        <v>6.3714</v>
       </c>
       <c r="F54">
-        <v>7.997599999999999</v>
+        <v>8.151400000000001</v>
       </c>
       <c r="G54">
         <v>2.94</v>
@@ -5703,37 +5703,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M54">
-        <v>1.88583408</v>
+        <v>1.92210012</v>
       </c>
       <c r="N54">
-        <v>-1.17083408</v>
+        <v>-1.20710012</v>
       </c>
       <c r="O54">
-        <v>-0.1873334528</v>
+        <v>-0.1931360192</v>
       </c>
       <c r="P54">
-        <v>-0.9835006271999999</v>
+        <v>-1.0139641008</v>
       </c>
       <c r="Q54">
-        <v>-0.6085006271999999</v>
+        <v>-0.6389641008000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1230441917978743</v>
+        <v>0.1246876852403823</v>
       </c>
       <c r="T54">
-        <v>1.063295375196425</v>
+        <v>1.085918681051668</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06066281292360567</v>
+        <v>0.05951823154768857</v>
       </c>
       <c r="W54">
-        <v>0.2214957087126138</v>
+        <v>0.2217656010010551</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3791425807725355</v>
+        <v>0.3719889471730536</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1761389805935388</v>
+        <v>0.1780389805935388</v>
       </c>
       <c r="C55">
-        <v>0.5909655027200262</v>
+        <v>0.3727662967760388</v>
       </c>
       <c r="D55">
-        <v>5.802365502720026</v>
+        <v>5.737966296776038</v>
       </c>
       <c r="E55">
-        <v>6.3714</v>
+        <v>6.525199999999999</v>
       </c>
       <c r="F55">
-        <v>8.151400000000001</v>
+        <v>8.305199999999999</v>
       </c>
       <c r="G55">
         <v>2.94</v>
@@ -5785,37 +5785,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M55">
-        <v>1.92210012</v>
+        <v>1.95836616</v>
       </c>
       <c r="N55">
-        <v>-1.20710012</v>
+        <v>-1.24336616</v>
       </c>
       <c r="O55">
-        <v>-0.1931360192</v>
+        <v>-0.1989385856</v>
       </c>
       <c r="P55">
-        <v>-1.0139641008</v>
+        <v>-1.0444275744</v>
       </c>
       <c r="Q55">
-        <v>-0.6389641008000002</v>
+        <v>-0.6694275743999998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1246876852403823</v>
+        <v>0.126402634919521</v>
       </c>
       <c r="T55">
-        <v>1.085918681051668</v>
+        <v>1.109525608900617</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.05951823154768857</v>
+        <v>0.05841604207458324</v>
       </c>
       <c r="W55">
-        <v>0.2217656010010551</v>
+        <v>0.2220254972788133</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3719889471730536</v>
+        <v>0.3651002629661453</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1780389805935388</v>
+        <v>0.1799389805935388</v>
       </c>
       <c r="C56">
-        <v>0.3727662967760388</v>
+        <v>0.1559809050660146</v>
       </c>
       <c r="D56">
-        <v>5.737966296776038</v>
+        <v>5.674980905066014</v>
       </c>
       <c r="E56">
-        <v>6.525199999999999</v>
+        <v>6.678999999999999</v>
       </c>
       <c r="F56">
-        <v>8.305199999999999</v>
+        <v>8.459</v>
       </c>
       <c r="G56">
         <v>2.94</v>
@@ -5867,37 +5867,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M56">
-        <v>1.95836616</v>
+        <v>1.9946322</v>
       </c>
       <c r="N56">
-        <v>-1.24336616</v>
+        <v>-1.2796322</v>
       </c>
       <c r="O56">
-        <v>-0.1989385856</v>
+        <v>-0.204741152</v>
       </c>
       <c r="P56">
-        <v>-1.0444275744</v>
+        <v>-1.074891048</v>
       </c>
       <c r="Q56">
-        <v>-0.6694275743999998</v>
+        <v>-0.699891048</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.126402634919521</v>
+        <v>0.1281938045843992</v>
       </c>
       <c r="T56">
-        <v>1.109525608900617</v>
+        <v>1.134181733542853</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.05841604207458324</v>
+        <v>0.05735393221868172</v>
       </c>
       <c r="W56">
-        <v>0.2220254972788133</v>
+        <v>0.2222759427828349</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3651002629661453</v>
+        <v>0.3584620763667608</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1799389805935388</v>
+        <v>0.1818389805935388</v>
       </c>
       <c r="C57">
-        <v>0.1559809050660146</v>
+        <v>-0.05943672501388342</v>
       </c>
       <c r="D57">
-        <v>5.674980905066014</v>
+        <v>5.613363274986116</v>
       </c>
       <c r="E57">
-        <v>6.678999999999999</v>
+        <v>6.8328</v>
       </c>
       <c r="F57">
-        <v>8.459</v>
+        <v>8.6128</v>
       </c>
       <c r="G57">
         <v>2.94</v>
@@ -5949,37 +5949,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M57">
-        <v>1.9946322</v>
+        <v>2.03089824</v>
       </c>
       <c r="N57">
-        <v>-1.2796322</v>
+        <v>-1.31589824</v>
       </c>
       <c r="O57">
-        <v>-0.204741152</v>
+        <v>-0.2105437184</v>
       </c>
       <c r="P57">
-        <v>-1.074891048</v>
+        <v>-1.1053545216</v>
       </c>
       <c r="Q57">
-        <v>-0.699891048</v>
+        <v>-0.7303545215999998</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1281938045843992</v>
+        <v>0.1300663910522265</v>
       </c>
       <c r="T57">
-        <v>1.134181733542853</v>
+        <v>1.159958591123373</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.05735393221868172</v>
+        <v>0.05632975485763384</v>
       </c>
       <c r="W57">
-        <v>0.2222759427828349</v>
+        <v>0.2225174438045699</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3584620763667608</v>
+        <v>0.3520609678602115</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1818389805935388</v>
+        <v>0.1837389805935388</v>
       </c>
       <c r="C58">
-        <v>-0.05943672501388342</v>
+        <v>-0.2735306674369209</v>
       </c>
       <c r="D58">
-        <v>5.613363274986116</v>
+        <v>5.553069332563079</v>
       </c>
       <c r="E58">
-        <v>6.8328</v>
+        <v>6.9866</v>
       </c>
       <c r="F58">
-        <v>8.6128</v>
+        <v>8.7666</v>
       </c>
       <c r="G58">
         <v>2.94</v>
@@ -6031,37 +6031,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M58">
-        <v>2.03089824</v>
+        <v>2.06716428</v>
       </c>
       <c r="N58">
-        <v>-1.31589824</v>
+        <v>-1.35216428</v>
       </c>
       <c r="O58">
-        <v>-0.2105437184</v>
+        <v>-0.2163462848</v>
       </c>
       <c r="P58">
-        <v>-1.1053545216</v>
+        <v>-1.1358179952</v>
       </c>
       <c r="Q58">
-        <v>-0.7303545215999998</v>
+        <v>-0.7608179952</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1300663910522265</v>
+        <v>0.132026074565069</v>
       </c>
       <c r="T58">
-        <v>1.159958591123373</v>
+        <v>1.186934372312288</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.05632975485763384</v>
+        <v>0.05534151354434202</v>
       </c>
       <c r="W58">
-        <v>0.2225174438045699</v>
+        <v>0.2227504711062442</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3520609678602115</v>
+        <v>0.3458844596521375</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1837389805935388</v>
+        <v>0.1856389805935388</v>
       </c>
       <c r="C59">
-        <v>-0.2735306674369209</v>
+        <v>-0.4863431226803137</v>
       </c>
       <c r="D59">
-        <v>5.553069332563079</v>
+        <v>5.494056877319687</v>
       </c>
       <c r="E59">
-        <v>6.9866</v>
+        <v>7.140400000000001</v>
       </c>
       <c r="F59">
-        <v>8.7666</v>
+        <v>8.920400000000001</v>
       </c>
       <c r="G59">
         <v>2.94</v>
@@ -6113,37 +6113,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M59">
-        <v>2.06716428</v>
+        <v>2.10343032</v>
       </c>
       <c r="N59">
-        <v>-1.35216428</v>
+        <v>-1.38843032</v>
       </c>
       <c r="O59">
-        <v>-0.2163462848</v>
+        <v>-0.2221488512</v>
       </c>
       <c r="P59">
-        <v>-1.1358179952</v>
+        <v>-1.1662814688</v>
       </c>
       <c r="Q59">
-        <v>-0.7608179952</v>
+        <v>-0.7912814688000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.132026074565069</v>
+        <v>0.1340790763404278</v>
       </c>
       <c r="T59">
-        <v>1.186934372312288</v>
+        <v>1.2151947145102</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.05534151354434202</v>
+        <v>0.05438734951771543</v>
       </c>
       <c r="W59">
-        <v>0.2227504711062442</v>
+        <v>0.2229754629837227</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3458844596521375</v>
+        <v>0.3399209344857214</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1856389805935388</v>
+        <v>0.1875389805935389</v>
       </c>
       <c r="C60">
-        <v>-0.4863431226803119</v>
+        <v>-0.6979145162266267</v>
       </c>
       <c r="D60">
-        <v>5.494056877319687</v>
+        <v>5.436285483773372</v>
       </c>
       <c r="E60">
-        <v>7.140399999999999</v>
+        <v>7.294199999999999</v>
       </c>
       <c r="F60">
-        <v>8.920399999999999</v>
+        <v>9.074199999999999</v>
       </c>
       <c r="G60">
         <v>2.94</v>
@@ -6195,37 +6195,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M60">
-        <v>2.10343032</v>
+        <v>2.13969636</v>
       </c>
       <c r="N60">
-        <v>-1.38843032</v>
+        <v>-1.42469636</v>
       </c>
       <c r="O60">
-        <v>-0.2221488511999999</v>
+        <v>-0.2279514176</v>
       </c>
       <c r="P60">
-        <v>-1.1662814688</v>
+        <v>-1.1967449424</v>
       </c>
       <c r="Q60">
-        <v>-0.7912814687999998</v>
+        <v>-0.8217449423999998</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1340790763404278</v>
+        <v>0.1362322245438528</v>
       </c>
       <c r="T60">
-        <v>1.2151947145102</v>
+        <v>1.244833609986058</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.05438734951771543</v>
+        <v>0.05346553003436433</v>
       </c>
       <c r="W60">
-        <v>0.2229754629837227</v>
+        <v>0.2231928280178969</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3399209344857215</v>
+        <v>0.334159562714777</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1875389805935389</v>
+        <v>0.1894389805935388</v>
       </c>
       <c r="C61">
-        <v>-0.6979145162266267</v>
+        <v>-0.9082835909152784</v>
       </c>
       <c r="D61">
-        <v>5.436285483773372</v>
+        <v>5.379716409084722</v>
       </c>
       <c r="E61">
-        <v>7.294199999999999</v>
+        <v>7.448</v>
       </c>
       <c r="F61">
-        <v>9.074199999999999</v>
+        <v>9.228</v>
       </c>
       <c r="G61">
         <v>2.94</v>
@@ -6277,37 +6277,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M61">
-        <v>2.13969636</v>
+        <v>2.1759624</v>
       </c>
       <c r="N61">
-        <v>-1.42469636</v>
+        <v>-1.4609624</v>
       </c>
       <c r="O61">
-        <v>-0.2279514176</v>
+        <v>-0.233753984</v>
       </c>
       <c r="P61">
-        <v>-1.1967449424</v>
+        <v>-1.227208416</v>
       </c>
       <c r="Q61">
-        <v>-0.8217449423999998</v>
+        <v>-0.8522084159999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1362322245438528</v>
+        <v>0.1384930301574491</v>
       </c>
       <c r="T61">
-        <v>1.244833609986058</v>
+        <v>1.27595445023571</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05346553003436433</v>
+        <v>0.05257443786712492</v>
       </c>
       <c r="W61">
-        <v>0.2231928280178969</v>
+        <v>0.223402947550932</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.334159562714777</v>
+        <v>0.3285902366695307</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1894389805935388</v>
+        <v>0.1913389805935388</v>
       </c>
       <c r="C62">
-        <v>-0.9082835909152784</v>
+        <v>-1.117487493587422</v>
       </c>
       <c r="D62">
-        <v>5.379716409084722</v>
+        <v>5.324312506412577</v>
       </c>
       <c r="E62">
-        <v>7.448</v>
+        <v>7.601799999999998</v>
       </c>
       <c r="F62">
-        <v>9.228</v>
+        <v>9.381799999999998</v>
       </c>
       <c r="G62">
         <v>2.94</v>
@@ -6359,37 +6359,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M62">
-        <v>2.1759624</v>
+        <v>2.21222844</v>
       </c>
       <c r="N62">
-        <v>-1.4609624</v>
+        <v>-1.49722844</v>
       </c>
       <c r="O62">
-        <v>-0.233753984</v>
+        <v>-0.2395565503999999</v>
       </c>
       <c r="P62">
-        <v>-1.227208416</v>
+        <v>-1.2576718896</v>
       </c>
       <c r="Q62">
-        <v>-0.8522084159999999</v>
+        <v>-0.8826718895999996</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1384930301574491</v>
+        <v>0.1408697745204606</v>
       </c>
       <c r="T62">
-        <v>1.27595445023571</v>
+        <v>1.308671231010984</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05257443786712492</v>
+        <v>0.05171256183651633</v>
       </c>
       <c r="W62">
-        <v>0.223402947550932</v>
+        <v>0.2236061779189495</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3285902366695307</v>
+        <v>0.323203511478227</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1913389805935388</v>
+        <v>0.1932389805935388</v>
       </c>
       <c r="C63">
-        <v>-1.117487493587422</v>
+        <v>-1.325561856431476</v>
       </c>
       <c r="D63">
-        <v>5.324312506412577</v>
+        <v>5.270038143568524</v>
       </c>
       <c r="E63">
-        <v>7.601799999999998</v>
+        <v>7.755599999999998</v>
       </c>
       <c r="F63">
-        <v>9.381799999999998</v>
+        <v>9.535599999999999</v>
       </c>
       <c r="G63">
         <v>2.94</v>
@@ -6441,37 +6441,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M63">
-        <v>2.21222844</v>
+        <v>2.24849448</v>
       </c>
       <c r="N63">
-        <v>-1.49722844</v>
+        <v>-1.53349448</v>
       </c>
       <c r="O63">
-        <v>-0.2395565503999999</v>
+        <v>-0.2453591167999999</v>
       </c>
       <c r="P63">
-        <v>-1.2576718896</v>
+        <v>-1.2881353632</v>
       </c>
       <c r="Q63">
-        <v>-0.8826718895999996</v>
+        <v>-0.9131353631999997</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1408697745204606</v>
+        <v>0.1433716106920517</v>
       </c>
       <c r="T63">
-        <v>1.308671231010984</v>
+        <v>1.343109947616537</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05171256183651633</v>
+        <v>0.05087848825850799</v>
       </c>
       <c r="W63">
-        <v>0.2236061779189495</v>
+        <v>0.2238028524686438</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.323203511478227</v>
+        <v>0.3179905516156749</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1932389805935388</v>
+        <v>0.1951389805935388</v>
       </c>
       <c r="C64">
-        <v>-1.325561856431476</v>
+        <v>-1.532540873403562</v>
       </c>
       <c r="D64">
-        <v>5.270038143568524</v>
+        <v>5.216859126596438</v>
       </c>
       <c r="E64">
-        <v>7.755599999999998</v>
+        <v>7.909399999999999</v>
       </c>
       <c r="F64">
-        <v>9.535599999999999</v>
+        <v>9.689399999999999</v>
       </c>
       <c r="G64">
         <v>2.94</v>
@@ -6523,37 +6523,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M64">
-        <v>2.24849448</v>
+        <v>2.28476052</v>
       </c>
       <c r="N64">
-        <v>-1.53349448</v>
+        <v>-1.56976052</v>
       </c>
       <c r="O64">
-        <v>-0.2453591167999999</v>
+        <v>-0.2511616832</v>
       </c>
       <c r="P64">
-        <v>-1.2881353632</v>
+        <v>-1.3185988368</v>
       </c>
       <c r="Q64">
-        <v>-0.9131353631999997</v>
+        <v>-0.9435988367999997</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1433716106920517</v>
+        <v>0.1460086812512963</v>
       </c>
       <c r="T64">
-        <v>1.343109947616537</v>
+        <v>1.379410216471038</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05087848825850799</v>
+        <v>0.05007089320678564</v>
       </c>
       <c r="W64">
-        <v>0.2238028524686438</v>
+        <v>0.22399328338184</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3179905516156749</v>
+        <v>0.3129430825424102</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1951389805935388</v>
+        <v>0.1970389805935388</v>
       </c>
       <c r="C65">
-        <v>-1.532540873403562</v>
+        <v>-1.738457372067327</v>
       </c>
       <c r="D65">
-        <v>5.216859126596438</v>
+        <v>5.164742627932673</v>
       </c>
       <c r="E65">
-        <v>7.909399999999999</v>
+        <v>8.0632</v>
       </c>
       <c r="F65">
-        <v>9.689399999999999</v>
+        <v>9.8432</v>
       </c>
       <c r="G65">
         <v>2.94</v>
@@ -6605,37 +6605,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M65">
-        <v>2.28476052</v>
+        <v>2.32102656</v>
       </c>
       <c r="N65">
-        <v>-1.56976052</v>
+        <v>-1.60602656</v>
       </c>
       <c r="O65">
-        <v>-0.2511616832</v>
+        <v>-0.2569642496</v>
       </c>
       <c r="P65">
-        <v>-1.3185988368</v>
+        <v>-1.3490623104</v>
       </c>
       <c r="Q65">
-        <v>-0.9435988367999997</v>
+        <v>-0.9740623103999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1460086812512963</v>
+        <v>0.148792255730499</v>
       </c>
       <c r="T65">
-        <v>1.379410216471038</v>
+        <v>1.417727166928566</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05007089320678564</v>
+        <v>0.04928853550042961</v>
       </c>
       <c r="W65">
-        <v>0.22399328338184</v>
+        <v>0.2241777633289987</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3129430825424102</v>
+        <v>0.308053346877685</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1970389805935388</v>
+        <v>0.1989389805935388</v>
       </c>
       <c r="C66">
-        <v>-1.738457372067327</v>
+        <v>-1.943342881170254</v>
       </c>
       <c r="D66">
-        <v>5.164742627932673</v>
+        <v>5.113657118829745</v>
       </c>
       <c r="E66">
-        <v>8.0632</v>
+        <v>8.217000000000001</v>
       </c>
       <c r="F66">
-        <v>9.8432</v>
+        <v>9.997</v>
       </c>
       <c r="G66">
         <v>2.94</v>
@@ -6687,37 +6687,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M66">
-        <v>2.32102656</v>
+        <v>2.3572926</v>
       </c>
       <c r="N66">
-        <v>-1.60602656</v>
+        <v>-1.6422926</v>
       </c>
       <c r="O66">
-        <v>-0.2569642496</v>
+        <v>-0.262766816</v>
       </c>
       <c r="P66">
-        <v>-1.3490623104</v>
+        <v>-1.379525784</v>
       </c>
       <c r="Q66">
-        <v>-0.9740623103999999</v>
+        <v>-1.004525784</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.148792255730499</v>
+        <v>0.1517348916085133</v>
       </c>
       <c r="T66">
-        <v>1.417727166928566</v>
+        <v>1.45823365741224</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04928853550042961</v>
+        <v>0.04853025033888454</v>
       </c>
       <c r="W66">
-        <v>0.2241777633289987</v>
+        <v>0.224356566970091</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.308053346877685</v>
+        <v>0.3033140646180283</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1989389805935388</v>
+        <v>0.2008389805935388</v>
       </c>
       <c r="C67">
-        <v>-1.943342881170254</v>
+        <v>-2.147227694248802</v>
       </c>
       <c r="D67">
-        <v>5.113657118829745</v>
+        <v>5.063572305751199</v>
       </c>
       <c r="E67">
-        <v>8.217000000000001</v>
+        <v>8.370800000000001</v>
       </c>
       <c r="F67">
-        <v>9.997</v>
+        <v>10.1508</v>
       </c>
       <c r="G67">
         <v>2.94</v>
@@ -6769,37 +6769,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M67">
-        <v>2.3572926</v>
+        <v>2.39355864</v>
       </c>
       <c r="N67">
-        <v>-1.6422926</v>
+        <v>-1.67855864</v>
       </c>
       <c r="O67">
-        <v>-0.262766816</v>
+        <v>-0.2685693824</v>
       </c>
       <c r="P67">
-        <v>-1.379525784</v>
+        <v>-1.4099892576</v>
       </c>
       <c r="Q67">
-        <v>-1.004525784</v>
+        <v>-1.0349892576</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1517348916085133</v>
+        <v>0.154850623714646</v>
       </c>
       <c r="T67">
-        <v>1.45823365741224</v>
+        <v>1.501122882630247</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.04853025033888454</v>
+        <v>0.0477949435155681</v>
       </c>
       <c r="W67">
-        <v>0.224356566970091</v>
+        <v>0.2245299523190291</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3033140646180283</v>
+        <v>0.2987183969723006</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2008389805935388</v>
+        <v>0.2027389805935388</v>
       </c>
       <c r="C68">
-        <v>-2.147227694248802</v>
+        <v>-2.350140929531944</v>
       </c>
       <c r="D68">
-        <v>5.063572305751199</v>
+        <v>5.014459070468056</v>
       </c>
       <c r="E68">
-        <v>8.370800000000001</v>
+        <v>8.524600000000001</v>
       </c>
       <c r="F68">
-        <v>10.1508</v>
+        <v>10.3046</v>
       </c>
       <c r="G68">
         <v>2.94</v>
@@ -6851,37 +6851,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M68">
-        <v>2.39355864</v>
+        <v>2.42982468</v>
       </c>
       <c r="N68">
-        <v>-1.67855864</v>
+        <v>-1.71482468</v>
       </c>
       <c r="O68">
-        <v>-0.2685693824</v>
+        <v>-0.2743719488</v>
       </c>
       <c r="P68">
-        <v>-1.4099892576</v>
+        <v>-1.4404527312</v>
       </c>
       <c r="Q68">
-        <v>-1.0349892576</v>
+        <v>-1.0654527312</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.154850623714646</v>
+        <v>0.1581551880696353</v>
       </c>
       <c r="T68">
-        <v>1.501122882630247</v>
+        <v>1.546611454831163</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0477949435155681</v>
+        <v>0.0470815861496641</v>
       </c>
       <c r="W68">
-        <v>0.2245299523190291</v>
+        <v>0.2246981619859092</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2987183969723006</v>
+        <v>0.2942599134354006</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2027389805935388</v>
+        <v>0.2046389805935388</v>
       </c>
       <c r="C69">
-        <v>-2.350140929531944</v>
+        <v>-2.552110586392114</v>
       </c>
       <c r="D69">
-        <v>5.014459070468056</v>
+        <v>4.966289413607885</v>
       </c>
       <c r="E69">
-        <v>8.524600000000001</v>
+        <v>8.6784</v>
       </c>
       <c r="F69">
-        <v>10.3046</v>
+        <v>10.4584</v>
       </c>
       <c r="G69">
         <v>2.94</v>
@@ -6933,37 +6933,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M69">
-        <v>2.42982468</v>
+        <v>2.46609072</v>
       </c>
       <c r="N69">
-        <v>-1.71482468</v>
+        <v>-1.75109072</v>
       </c>
       <c r="O69">
-        <v>-0.2743719488</v>
+        <v>-0.2801745152</v>
       </c>
       <c r="P69">
-        <v>-1.4404527312</v>
+        <v>-1.4709162048</v>
       </c>
       <c r="Q69">
-        <v>-1.0654527312</v>
+        <v>-1.0959162048</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1581551880696353</v>
+        <v>0.1616662876968114</v>
       </c>
       <c r="T69">
-        <v>1.546611454831163</v>
+        <v>1.594943062794637</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.0470815861496641</v>
+        <v>0.04638920988275728</v>
       </c>
       <c r="W69">
-        <v>0.2246981619859092</v>
+        <v>0.2248614243096458</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2942599134354006</v>
+        <v>0.289932561767233</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2046389805935388</v>
+        <v>0.2065389805935389</v>
       </c>
       <c r="C70">
-        <v>-2.552110586392114</v>
+        <v>-2.753163598573407</v>
       </c>
       <c r="D70">
-        <v>4.966289413607885</v>
+        <v>4.919036401426593</v>
       </c>
       <c r="E70">
-        <v>8.6784</v>
+        <v>8.8322</v>
       </c>
       <c r="F70">
-        <v>10.4584</v>
+        <v>10.6122</v>
       </c>
       <c r="G70">
         <v>2.94</v>
@@ -7015,37 +7015,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M70">
-        <v>2.46609072</v>
+        <v>2.50235676</v>
       </c>
       <c r="N70">
-        <v>-1.75109072</v>
+        <v>-1.78735676</v>
       </c>
       <c r="O70">
-        <v>-0.2801745152</v>
+        <v>-0.2859770816</v>
       </c>
       <c r="P70">
-        <v>-1.4709162048</v>
+        <v>-1.5013796784</v>
       </c>
       <c r="Q70">
-        <v>-1.0959162048</v>
+        <v>-1.1263796784</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1616662876968114</v>
+        <v>0.1654039098805795</v>
       </c>
       <c r="T70">
-        <v>1.594943062794637</v>
+        <v>1.646392839013819</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.04638920988275728</v>
+        <v>0.0457169024931521</v>
       </c>
       <c r="W70">
-        <v>0.2248614243096458</v>
+        <v>0.2250199543921148</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.289932561767233</v>
+        <v>0.2857306405822007</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2065389805935389</v>
+        <v>0.2084389805935388</v>
       </c>
       <c r="C71">
-        <v>-2.753163598573407</v>
+        <v>-2.953325884409701</v>
       </c>
       <c r="D71">
-        <v>4.919036401426593</v>
+        <v>4.8726741155903</v>
       </c>
       <c r="E71">
-        <v>8.8322</v>
+        <v>8.986000000000001</v>
       </c>
       <c r="F71">
-        <v>10.6122</v>
+        <v>10.766</v>
       </c>
       <c r="G71">
         <v>2.94</v>
@@ -7097,37 +7097,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M71">
-        <v>2.50235676</v>
+        <v>2.5386228</v>
       </c>
       <c r="N71">
-        <v>-1.78735676</v>
+        <v>-1.8236228</v>
       </c>
       <c r="O71">
-        <v>-0.2859770816</v>
+        <v>-0.291779648</v>
       </c>
       <c r="P71">
-        <v>-1.5013796784</v>
+        <v>-1.531843152</v>
       </c>
       <c r="Q71">
-        <v>-1.1263796784</v>
+        <v>-1.156843152</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1654039098805795</v>
+        <v>0.1693907068765989</v>
       </c>
       <c r="T71">
-        <v>1.646392839013819</v>
+        <v>1.70127260031428</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0457169024931521</v>
+        <v>0.04506380388610706</v>
       </c>
       <c r="W71">
-        <v>0.2250199543921148</v>
+        <v>0.2251739550436559</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2857306405822007</v>
+        <v>0.2816487742881691</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2084389805935388</v>
+        <v>0.2103389805935389</v>
       </c>
       <c r="C72">
-        <v>-2.953325884409701</v>
+        <v>-3.152622394229468</v>
       </c>
       <c r="D72">
-        <v>4.8726741155903</v>
+        <v>4.827177605770532</v>
       </c>
       <c r="E72">
-        <v>8.986000000000001</v>
+        <v>9.139800000000001</v>
       </c>
       <c r="F72">
-        <v>10.766</v>
+        <v>10.9198</v>
       </c>
       <c r="G72">
         <v>2.94</v>
@@ -7179,37 +7179,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M72">
-        <v>2.5386228</v>
+        <v>2.57488884</v>
       </c>
       <c r="N72">
-        <v>-1.8236228</v>
+        <v>-1.85988884</v>
       </c>
       <c r="O72">
-        <v>-0.291779648</v>
+        <v>-0.2975822144</v>
       </c>
       <c r="P72">
-        <v>-1.531843152</v>
+        <v>-1.5623066256</v>
       </c>
       <c r="Q72">
-        <v>-1.156843152</v>
+        <v>-1.1873066256</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1693907068765989</v>
+        <v>0.1736524553895851</v>
       </c>
       <c r="T72">
-        <v>1.70127260031428</v>
+        <v>1.759937172738911</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04506380388610706</v>
+        <v>0.04442910242292247</v>
       </c>
       <c r="W72">
-        <v>0.2251739550436559</v>
+        <v>0.2253236176486749</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2816487742881691</v>
+        <v>0.2776818901432654</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2103389805935388</v>
+        <v>0.2122389805935389</v>
       </c>
       <c r="C73">
-        <v>-3.152622394229466</v>
+        <v>-3.351077155129387</v>
       </c>
       <c r="D73">
-        <v>4.827177605770533</v>
+        <v>4.782522844870613</v>
       </c>
       <c r="E73">
-        <v>9.139799999999999</v>
+        <v>9.2936</v>
       </c>
       <c r="F73">
-        <v>10.9198</v>
+        <v>11.0736</v>
       </c>
       <c r="G73">
         <v>2.94</v>
@@ -7261,37 +7261,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M73">
-        <v>2.57488884</v>
+        <v>2.61115488</v>
       </c>
       <c r="N73">
-        <v>-1.85988884</v>
+        <v>-1.89615488</v>
       </c>
       <c r="O73">
-        <v>-0.2975822144</v>
+        <v>-0.3033847808</v>
       </c>
       <c r="P73">
-        <v>-1.5623066256</v>
+        <v>-1.5927700992</v>
       </c>
       <c r="Q73">
-        <v>-1.1873066256</v>
+        <v>-1.2177700992</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.173652455389585</v>
+        <v>0.1782186145106416</v>
       </c>
       <c r="T73">
-        <v>1.75993717273891</v>
+        <v>1.8227920717653</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04442910242292247</v>
+        <v>0.04381203155593744</v>
       </c>
       <c r="W73">
-        <v>0.2253236176486749</v>
+        <v>0.22546912295911</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2776818901432654</v>
+        <v>0.273825197224609</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2122389805935389</v>
+        <v>0.2141389805935388</v>
       </c>
       <c r="C74">
-        <v>-3.351077155129387</v>
+        <v>-3.548713313285637</v>
       </c>
       <c r="D74">
-        <v>4.782522844870613</v>
+        <v>4.738686686714363</v>
       </c>
       <c r="E74">
-        <v>9.2936</v>
+        <v>9.4474</v>
       </c>
       <c r="F74">
-        <v>11.0736</v>
+        <v>11.2274</v>
       </c>
       <c r="G74">
         <v>2.94</v>
@@ -7343,37 +7343,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M74">
-        <v>2.61115488</v>
+        <v>2.64742092</v>
       </c>
       <c r="N74">
-        <v>-1.89615488</v>
+        <v>-1.93242092</v>
       </c>
       <c r="O74">
-        <v>-0.3033847808</v>
+        <v>-0.3091873472</v>
       </c>
       <c r="P74">
-        <v>-1.5927700992</v>
+        <v>-1.6232335728</v>
       </c>
       <c r="Q74">
-        <v>-1.2177700992</v>
+        <v>-1.2482335728</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1782186145106416</v>
+        <v>0.1831230076406654</v>
       </c>
       <c r="T74">
-        <v>1.8227920717653</v>
+        <v>1.890302889238088</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04381203155593744</v>
+        <v>0.04321186674010268</v>
       </c>
       <c r="W74">
-        <v>0.22546912295911</v>
+        <v>0.2256106418226838</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.273825197224609</v>
+        <v>0.2700741671256417</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2141389805935388</v>
+        <v>0.2160389805935388</v>
       </c>
       <c r="C75">
-        <v>-3.548713313285637</v>
+        <v>-3.745553173959376</v>
       </c>
       <c r="D75">
-        <v>4.738686686714363</v>
+        <v>4.695646826040623</v>
       </c>
       <c r="E75">
-        <v>9.4474</v>
+        <v>9.6012</v>
       </c>
       <c r="F75">
-        <v>11.2274</v>
+        <v>11.3812</v>
       </c>
       <c r="G75">
         <v>2.94</v>
@@ -7425,37 +7425,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M75">
-        <v>2.64742092</v>
+        <v>2.68368696</v>
       </c>
       <c r="N75">
-        <v>-1.93242092</v>
+        <v>-1.96868696</v>
       </c>
       <c r="O75">
-        <v>-0.3091873472</v>
+        <v>-0.3149899136</v>
       </c>
       <c r="P75">
-        <v>-1.6232335728</v>
+        <v>-1.6536970464</v>
       </c>
       <c r="Q75">
-        <v>-1.2482335728</v>
+        <v>-1.2786970464</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1831230076406654</v>
+        <v>0.188404661780691</v>
       </c>
       <c r="T75">
-        <v>1.890302889238088</v>
+        <v>1.963006846516476</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04321186674010268</v>
+        <v>0.04262792259496614</v>
       </c>
       <c r="W75">
-        <v>0.2256106418226838</v>
+        <v>0.225748335852107</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2700741671256417</v>
+        <v>0.2664245162185384</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2160389805935388</v>
+        <v>0.2179389805935388</v>
       </c>
       <c r="C76">
-        <v>-3.745553173959376</v>
+        <v>-3.941618239341727</v>
       </c>
       <c r="D76">
-        <v>4.695646826040623</v>
+        <v>4.653381760658274</v>
       </c>
       <c r="E76">
-        <v>9.6012</v>
+        <v>9.755000000000001</v>
       </c>
       <c r="F76">
-        <v>11.3812</v>
+        <v>11.535</v>
       </c>
       <c r="G76">
         <v>2.94</v>
@@ -7507,37 +7507,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M76">
-        <v>2.68368696</v>
+        <v>2.719953</v>
       </c>
       <c r="N76">
-        <v>-1.96868696</v>
+        <v>-2.004953</v>
       </c>
       <c r="O76">
-        <v>-0.3149899136</v>
+        <v>-0.3207924800000001</v>
       </c>
       <c r="P76">
-        <v>-1.6536970464</v>
+        <v>-1.68416052</v>
       </c>
       <c r="Q76">
-        <v>-1.2786970464</v>
+        <v>-1.30916052</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.188404661780691</v>
+        <v>0.1941088482519186</v>
       </c>
       <c r="T76">
-        <v>1.963006846516476</v>
+        <v>2.041527120377136</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04262792259496614</v>
+        <v>0.04205955029369993</v>
       </c>
       <c r="W76">
-        <v>0.225748335852107</v>
+        <v>0.2258823580407456</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2664245162185384</v>
+        <v>0.2628721893356245</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2179389805935388</v>
+        <v>0.2198389805935388</v>
       </c>
       <c r="C77">
-        <v>-3.941618239341727</v>
+        <v>-4.136929244373137</v>
       </c>
       <c r="D77">
-        <v>4.653381760658274</v>
+        <v>4.611870755626862</v>
       </c>
       <c r="E77">
-        <v>9.755000000000001</v>
+        <v>9.908799999999999</v>
       </c>
       <c r="F77">
-        <v>11.535</v>
+        <v>11.6888</v>
       </c>
       <c r="G77">
         <v>2.94</v>
@@ -7589,37 +7589,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M77">
-        <v>2.719953</v>
+        <v>2.75621904</v>
       </c>
       <c r="N77">
-        <v>-2.004953</v>
+        <v>-2.04121904</v>
       </c>
       <c r="O77">
-        <v>-0.3207924800000001</v>
+        <v>-0.3265950464</v>
       </c>
       <c r="P77">
-        <v>-1.68416052</v>
+        <v>-1.7146239936</v>
       </c>
       <c r="Q77">
-        <v>-1.30916052</v>
+        <v>-1.3396239936</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1941088482519186</v>
+        <v>0.2002883835957486</v>
       </c>
       <c r="T77">
-        <v>2.041527120377136</v>
+        <v>2.12659075039285</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04205955029369993</v>
+        <v>0.04150613515825651</v>
       </c>
       <c r="W77">
-        <v>0.2258823580407456</v>
+        <v>0.2260128533296831</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2628721893356245</v>
+        <v>0.2594133447391033</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2198389805935388</v>
+        <v>0.2217389805935389</v>
       </c>
       <c r="C78">
-        <v>-4.136929244373137</v>
+        <v>-4.331506190662546</v>
       </c>
       <c r="D78">
-        <v>4.611870755626862</v>
+        <v>4.571093809337452</v>
       </c>
       <c r="E78">
-        <v>9.908799999999999</v>
+        <v>10.0626</v>
       </c>
       <c r="F78">
-        <v>11.6888</v>
+        <v>11.8426</v>
       </c>
       <c r="G78">
         <v>2.94</v>
@@ -7671,37 +7671,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M78">
-        <v>2.75621904</v>
+        <v>2.79248508</v>
       </c>
       <c r="N78">
-        <v>-2.04121904</v>
+        <v>-2.07748508</v>
       </c>
       <c r="O78">
-        <v>-0.3265950464</v>
+        <v>-0.3323976128</v>
       </c>
       <c r="P78">
-        <v>-1.7146239936</v>
+        <v>-1.7450874672</v>
       </c>
       <c r="Q78">
-        <v>-1.3396239936</v>
+        <v>-1.3700874672</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2002883835957486</v>
+        <v>0.207005269839042</v>
       </c>
       <c r="T78">
-        <v>2.12659075039285</v>
+        <v>2.219051217801235</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04150613515825651</v>
+        <v>0.04096709444191552</v>
       </c>
       <c r="W78">
-        <v>0.2260128533296831</v>
+        <v>0.2261399591305963</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2594133447391033</v>
+        <v>0.2560443402619721</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2217389805935389</v>
+        <v>0.2236389805935388</v>
       </c>
       <c r="C79">
-        <v>-4.331506190662546</v>
+        <v>-4.52536837862284</v>
       </c>
       <c r="D79">
-        <v>4.571093809337452</v>
+        <v>4.53103162137716</v>
       </c>
       <c r="E79">
-        <v>10.0626</v>
+        <v>10.2164</v>
       </c>
       <c r="F79">
-        <v>11.8426</v>
+        <v>11.9964</v>
       </c>
       <c r="G79">
         <v>2.94</v>
@@ -7753,37 +7753,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M79">
-        <v>2.79248508</v>
+        <v>2.82875112</v>
       </c>
       <c r="N79">
-        <v>-2.07748508</v>
+        <v>-2.11375112</v>
       </c>
       <c r="O79">
-        <v>-0.3323976128</v>
+        <v>-0.3382001792</v>
       </c>
       <c r="P79">
-        <v>-1.7450874672</v>
+        <v>-1.7755509408</v>
       </c>
       <c r="Q79">
-        <v>-1.3700874672</v>
+        <v>-1.4005509408</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.207005269839042</v>
+        <v>0.214332782104453</v>
       </c>
       <c r="T79">
-        <v>2.219051217801235</v>
+        <v>2.319917182246745</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04096709444191552</v>
+        <v>0.04044187528240378</v>
       </c>
       <c r="W79">
-        <v>0.2261399591305963</v>
+        <v>0.2262638058084092</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2560443402619721</v>
+        <v>0.2527617205150237</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2236389805935388</v>
+        <v>0.2255389805935389</v>
       </c>
       <c r="C80">
-        <v>-4.52536837862284</v>
+        <v>-4.718534437931183</v>
       </c>
       <c r="D80">
-        <v>4.53103162137716</v>
+        <v>4.491665562068817</v>
       </c>
       <c r="E80">
-        <v>10.2164</v>
+        <v>10.3702</v>
       </c>
       <c r="F80">
-        <v>11.9964</v>
+        <v>12.1502</v>
       </c>
       <c r="G80">
         <v>2.94</v>
@@ -7835,37 +7835,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M80">
-        <v>2.82875112</v>
+        <v>2.86501716</v>
       </c>
       <c r="N80">
-        <v>-2.11375112</v>
+        <v>-2.15001716</v>
       </c>
       <c r="O80">
-        <v>-0.3382001792</v>
+        <v>-0.3440027456</v>
       </c>
       <c r="P80">
-        <v>-1.7755509408</v>
+        <v>-1.8060144144</v>
       </c>
       <c r="Q80">
-        <v>-1.4005509408</v>
+        <v>-1.4310144144</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.214332782104453</v>
+        <v>0.2223581526808555</v>
       </c>
       <c r="T80">
-        <v>2.319917182246745</v>
+        <v>2.4303894290204</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04044187528240378</v>
+        <v>0.03992995281047462</v>
       </c>
       <c r="W80">
-        <v>0.2262638058084092</v>
+        <v>0.2263845171272901</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2527617205150237</v>
+        <v>0.2495622050654664</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2255389805935389</v>
+        <v>0.2274389805935388</v>
       </c>
       <c r="C81">
-        <v>-4.718534437931183</v>
+        <v>-4.911022356415144</v>
       </c>
       <c r="D81">
-        <v>4.491665562068817</v>
+        <v>4.452977643584856</v>
       </c>
       <c r="E81">
-        <v>10.3702</v>
+        <v>10.524</v>
       </c>
       <c r="F81">
-        <v>12.1502</v>
+        <v>12.304</v>
       </c>
       <c r="G81">
         <v>2.94</v>
@@ -7917,37 +7917,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M81">
-        <v>2.86501716</v>
+        <v>2.9012832</v>
       </c>
       <c r="N81">
-        <v>-2.15001716</v>
+        <v>-2.1862832</v>
       </c>
       <c r="O81">
-        <v>-0.3440027456</v>
+        <v>-0.349805312</v>
       </c>
       <c r="P81">
-        <v>-1.8060144144</v>
+        <v>-1.836477888</v>
       </c>
       <c r="Q81">
-        <v>-1.4310144144</v>
+        <v>-1.461477888</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2223581526808555</v>
+        <v>0.2311860603148983</v>
       </c>
       <c r="T81">
-        <v>2.4303894290204</v>
+        <v>2.55190890047142</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03992995281047462</v>
+        <v>0.03943082840034368</v>
       </c>
       <c r="W81">
-        <v>0.2263845171272901</v>
+        <v>0.2265022106631989</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2495622050654664</v>
+        <v>0.2464426775021481</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2274389805935388</v>
+        <v>0.2293389805935389</v>
       </c>
       <c r="C82">
-        <v>-4.911022356415144</v>
+        <v>-5.102849507458753</v>
       </c>
       <c r="D82">
-        <v>4.452977643584856</v>
+        <v>4.414950492541247</v>
       </c>
       <c r="E82">
-        <v>10.524</v>
+        <v>10.6778</v>
       </c>
       <c r="F82">
-        <v>12.304</v>
+        <v>12.4578</v>
       </c>
       <c r="G82">
         <v>2.94</v>
@@ -7999,37 +7999,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M82">
-        <v>2.9012832</v>
+        <v>2.93754924</v>
       </c>
       <c r="N82">
-        <v>-2.1862832</v>
+        <v>-2.22254924</v>
       </c>
       <c r="O82">
-        <v>-0.349805312</v>
+        <v>-0.3556078784</v>
       </c>
       <c r="P82">
-        <v>-1.836477888</v>
+        <v>-1.8669413616</v>
       </c>
       <c r="Q82">
-        <v>-1.461477888</v>
+        <v>-1.4919413616</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2311860603148983</v>
+        <v>0.2409432213841035</v>
       </c>
       <c r="T82">
-        <v>2.55190890047142</v>
+        <v>2.686219895233074</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03943082840034368</v>
+        <v>0.03894402804972216</v>
       </c>
       <c r="W82">
-        <v>0.2265022106631989</v>
+        <v>0.2266169981858755</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2464426775021481</v>
+        <v>0.2434001753107634</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2293389805935389</v>
+        <v>0.2312389805935388</v>
       </c>
       <c r="C83">
-        <v>-5.102849507458753</v>
+        <v>-5.294032676016199</v>
       </c>
       <c r="D83">
-        <v>4.414950492541247</v>
+        <v>4.3775673239838</v>
       </c>
       <c r="E83">
-        <v>10.6778</v>
+        <v>10.8316</v>
       </c>
       <c r="F83">
-        <v>12.4578</v>
+        <v>12.6116</v>
       </c>
       <c r="G83">
         <v>2.94</v>
@@ -8081,37 +8081,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M83">
-        <v>2.93754924</v>
+        <v>2.97381528</v>
       </c>
       <c r="N83">
-        <v>-2.22254924</v>
+        <v>-2.258815279999999</v>
       </c>
       <c r="O83">
-        <v>-0.3556078784</v>
+        <v>-0.3614104447999999</v>
       </c>
       <c r="P83">
-        <v>-1.8669413616</v>
+        <v>-1.897404835199999</v>
       </c>
       <c r="Q83">
-        <v>-1.4919413616</v>
+        <v>-1.522404835199999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2409432213841035</v>
+        <v>0.2517845114609981</v>
       </c>
       <c r="T83">
-        <v>2.686219895233074</v>
+        <v>2.835454333857134</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03894402804972216</v>
+        <v>0.03846910087838409</v>
       </c>
       <c r="W83">
-        <v>0.2266169981858755</v>
+        <v>0.2267289860128771</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2434001753107634</v>
+        <v>0.2404318804899006</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2312389805935388</v>
+        <v>0.2331389805935388</v>
       </c>
       <c r="C84">
-        <v>-5.294032676016199</v>
+        <v>-5.484588083315053</v>
       </c>
       <c r="D84">
-        <v>4.3775673239838</v>
+        <v>4.340811916684946</v>
       </c>
       <c r="E84">
-        <v>10.8316</v>
+        <v>10.9854</v>
       </c>
       <c r="F84">
-        <v>12.6116</v>
+        <v>12.7654</v>
       </c>
       <c r="G84">
         <v>2.94</v>
@@ -8163,37 +8163,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M84">
-        <v>2.97381528</v>
+        <v>3.01008132</v>
       </c>
       <c r="N84">
-        <v>-2.258815279999999</v>
+        <v>-2.29508132</v>
       </c>
       <c r="O84">
-        <v>-0.3614104447999999</v>
+        <v>-0.3672130111999999</v>
       </c>
       <c r="P84">
-        <v>-1.897404835199999</v>
+        <v>-1.927868308799999</v>
       </c>
       <c r="Q84">
-        <v>-1.522404835199999</v>
+        <v>-1.552868308799999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2517845114609981</v>
+        <v>0.2639012474292922</v>
       </c>
       <c r="T84">
-        <v>2.835454333857134</v>
+        <v>3.002245765260495</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03846910087838409</v>
+        <v>0.03800561773527102</v>
       </c>
       <c r="W84">
-        <v>0.2267289860128771</v>
+        <v>0.2268382753380231</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2404318804899006</v>
+        <v>0.237535110845444</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2331389805935388</v>
+        <v>0.2350389805935388</v>
       </c>
       <c r="C85">
-        <v>-5.484588083315053</v>
+        <v>-5.67453141032529</v>
       </c>
       <c r="D85">
-        <v>4.340811916684946</v>
+        <v>4.30466858967471</v>
       </c>
       <c r="E85">
-        <v>10.9854</v>
+        <v>11.1392</v>
       </c>
       <c r="F85">
-        <v>12.7654</v>
+        <v>12.9192</v>
       </c>
       <c r="G85">
         <v>2.94</v>
@@ -8245,37 +8245,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M85">
-        <v>3.01008132</v>
+        <v>3.04634736</v>
       </c>
       <c r="N85">
-        <v>-2.29508132</v>
+        <v>-2.33134736</v>
       </c>
       <c r="O85">
-        <v>-0.3672130111999999</v>
+        <v>-0.3730155775999999</v>
       </c>
       <c r="P85">
-        <v>-1.927868308799999</v>
+        <v>-1.9583317824</v>
       </c>
       <c r="Q85">
-        <v>-1.552868308799999</v>
+        <v>-1.5833317824</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2639012474292922</v>
+        <v>0.2775325753936229</v>
       </c>
       <c r="T85">
-        <v>3.002245765260495</v>
+        <v>3.189886125589276</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03800561773527102</v>
+        <v>0.03755316990508922</v>
       </c>
       <c r="W85">
-        <v>0.2268382753380231</v>
+        <v>0.22694496253638</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.237535110845444</v>
+        <v>0.2347073119068077</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2350389805935388</v>
+        <v>0.2369389805935388</v>
       </c>
       <c r="C86">
-        <v>-5.674531410325287</v>
+        <v>-5.863877820065579</v>
       </c>
       <c r="D86">
-        <v>4.304668589674711</v>
+        <v>4.269122179934421</v>
       </c>
       <c r="E86">
-        <v>11.1392</v>
+        <v>11.293</v>
       </c>
       <c r="F86">
-        <v>12.9192</v>
+        <v>13.073</v>
       </c>
       <c r="G86">
         <v>2.94</v>
@@ -8327,37 +8327,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M86">
-        <v>3.04634736</v>
+        <v>3.0826134</v>
       </c>
       <c r="N86">
-        <v>-2.33134736</v>
+        <v>-2.3676134</v>
       </c>
       <c r="O86">
-        <v>-0.3730155775999999</v>
+        <v>-0.378818144</v>
       </c>
       <c r="P86">
-        <v>-1.9583317824</v>
+        <v>-1.988795256</v>
       </c>
       <c r="Q86">
-        <v>-1.5833317824</v>
+        <v>-1.613795256</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2775325753936227</v>
+        <v>0.2929814137531976</v>
       </c>
       <c r="T86">
-        <v>3.189886125589274</v>
+        <v>3.402545200628559</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03755316990508923</v>
+        <v>0.03711136790620582</v>
       </c>
       <c r="W86">
-        <v>0.22694496253638</v>
+        <v>0.2270491394477167</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2347073119068076</v>
+        <v>0.2319460494137864</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2369389805935388</v>
+        <v>0.2388389805935389</v>
       </c>
       <c r="C87">
-        <v>-5.863877820065579</v>
+        <v>-6.052641978813423</v>
       </c>
       <c r="D87">
-        <v>4.269122179934421</v>
+        <v>4.234158021186576</v>
       </c>
       <c r="E87">
-        <v>11.293</v>
+        <v>11.4468</v>
       </c>
       <c r="F87">
-        <v>13.073</v>
+        <v>13.2268</v>
       </c>
       <c r="G87">
         <v>2.94</v>
@@ -8409,37 +8409,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M87">
-        <v>3.0826134</v>
+        <v>3.11887944</v>
       </c>
       <c r="N87">
-        <v>-2.3676134</v>
+        <v>-2.40387944</v>
       </c>
       <c r="O87">
-        <v>-0.378818144</v>
+        <v>-0.3846207104</v>
       </c>
       <c r="P87">
-        <v>-1.988795256</v>
+        <v>-2.0192587296</v>
       </c>
       <c r="Q87">
-        <v>-1.613795256</v>
+        <v>-1.6442587296</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2929814137531976</v>
+        <v>0.3106372290212833</v>
       </c>
       <c r="T87">
-        <v>3.402545200628559</v>
+        <v>3.645584143530599</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03711136790620582</v>
+        <v>0.03667984037241273</v>
       </c>
       <c r="W87">
-        <v>0.2270491394477167</v>
+        <v>0.2271508936401851</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2319460494137864</v>
+        <v>0.2292490023275795</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2388389805935389</v>
+        <v>0.2407389805935388</v>
       </c>
       <c r="C88">
-        <v>-6.052641978813423</v>
+        <v>-6.240838076281474</v>
       </c>
       <c r="D88">
-        <v>4.234158021186576</v>
+        <v>4.199761923718526</v>
       </c>
       <c r="E88">
-        <v>11.4468</v>
+        <v>11.6006</v>
       </c>
       <c r="F88">
-        <v>13.2268</v>
+        <v>13.3806</v>
       </c>
       <c r="G88">
         <v>2.94</v>
@@ -8491,37 +8491,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M88">
-        <v>3.11887944</v>
+        <v>3.15514548</v>
       </c>
       <c r="N88">
-        <v>-2.40387944</v>
+        <v>-2.44014548</v>
       </c>
       <c r="O88">
-        <v>-0.3846207104</v>
+        <v>-0.3904232768</v>
       </c>
       <c r="P88">
-        <v>-2.0192587296</v>
+        <v>-2.0497222032</v>
       </c>
       <c r="Q88">
-        <v>-1.6442587296</v>
+        <v>-1.6747222032</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3106372290212833</v>
+        <v>0.3310093235613819</v>
       </c>
       <c r="T88">
-        <v>3.645584143530599</v>
+        <v>3.926013693032953</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03667984037241273</v>
+        <v>0.03625823301181029</v>
       </c>
       <c r="W88">
-        <v>0.2271508936401851</v>
+        <v>0.2272503086558151</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2292490023275795</v>
+        <v>0.2266139563238142</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2407389805935388</v>
+        <v>0.2426389805935388</v>
       </c>
       <c r="C89">
-        <v>-6.240838076281474</v>
+        <v>-6.428479844818392</v>
       </c>
       <c r="D89">
-        <v>4.199761923718526</v>
+        <v>4.165920155181608</v>
       </c>
       <c r="E89">
-        <v>11.6006</v>
+        <v>11.7544</v>
       </c>
       <c r="F89">
-        <v>13.3806</v>
+        <v>13.5344</v>
       </c>
       <c r="G89">
         <v>2.94</v>
@@ -8573,37 +8573,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M89">
-        <v>3.15514548</v>
+        <v>3.19141152</v>
       </c>
       <c r="N89">
-        <v>-2.44014548</v>
+        <v>-2.47641152</v>
       </c>
       <c r="O89">
-        <v>-0.3904232768</v>
+        <v>-0.3962258432</v>
       </c>
       <c r="P89">
-        <v>-2.0497222032</v>
+        <v>-2.0801856768</v>
       </c>
       <c r="Q89">
-        <v>-1.6747222032</v>
+        <v>-1.7051856768</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3310093235613819</v>
+        <v>0.3547767671914971</v>
       </c>
       <c r="T89">
-        <v>3.926013693032953</v>
+        <v>4.253181500785699</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03625823301181029</v>
+        <v>0.03584620763667608</v>
       </c>
       <c r="W89">
-        <v>0.2272503086558151</v>
+        <v>0.2273474642392718</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2266139563238142</v>
+        <v>0.2240387977292254</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2426389805935388</v>
+        <v>0.2445389805935388</v>
       </c>
       <c r="C90">
-        <v>-6.428479844818392</v>
+        <v>-6.615580577688798</v>
       </c>
       <c r="D90">
-        <v>4.165920155181608</v>
+        <v>4.132619422311203</v>
       </c>
       <c r="E90">
-        <v>11.7544</v>
+        <v>11.9082</v>
       </c>
       <c r="F90">
-        <v>13.5344</v>
+        <v>13.6882</v>
       </c>
       <c r="G90">
         <v>2.94</v>
@@ -8655,37 +8655,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M90">
-        <v>3.19141152</v>
+        <v>3.22767756</v>
       </c>
       <c r="N90">
-        <v>-2.47641152</v>
+        <v>-2.51267756</v>
       </c>
       <c r="O90">
-        <v>-0.3962258432</v>
+        <v>-0.4020284096</v>
       </c>
       <c r="P90">
-        <v>-2.0801856768</v>
+        <v>-2.1106491504</v>
       </c>
       <c r="Q90">
-        <v>-1.7051856768</v>
+        <v>-1.7356491504</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3547767671914971</v>
+        <v>0.3828655642089059</v>
       </c>
       <c r="T90">
-        <v>4.253181500785699</v>
+        <v>4.63983436449349</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03584620763667608</v>
+        <v>0.0354434412587359</v>
       </c>
       <c r="W90">
-        <v>0.2273474642392718</v>
+        <v>0.2274424365511901</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2240387977292254</v>
+        <v>0.2215215078670993</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2445389805935388</v>
+        <v>0.2464389805935388</v>
       </c>
       <c r="C91">
-        <v>-6.615580577688798</v>
+        <v>-6.802153146483398</v>
       </c>
       <c r="D91">
-        <v>4.132619422311203</v>
+        <v>4.099846853516601</v>
       </c>
       <c r="E91">
-        <v>11.9082</v>
+        <v>12.062</v>
       </c>
       <c r="F91">
-        <v>13.6882</v>
+        <v>13.842</v>
       </c>
       <c r="G91">
         <v>2.94</v>
@@ -8737,37 +8737,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M91">
-        <v>3.22767756</v>
+        <v>3.2639436</v>
       </c>
       <c r="N91">
-        <v>-2.51267756</v>
+        <v>-2.548943599999999</v>
       </c>
       <c r="O91">
-        <v>-0.4020284096</v>
+        <v>-0.4078309759999999</v>
       </c>
       <c r="P91">
-        <v>-2.1106491504</v>
+        <v>-2.141112623999999</v>
       </c>
       <c r="Q91">
-        <v>-1.7356491504</v>
+        <v>-1.766112623999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3828655642089059</v>
+        <v>0.4165721206297966</v>
       </c>
       <c r="T91">
-        <v>4.63983436449349</v>
+        <v>5.103817800942839</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0354434412587359</v>
+        <v>0.03504962524474995</v>
       </c>
       <c r="W91">
-        <v>0.2274424365511901</v>
+        <v>0.227535298367288</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2215215078670993</v>
+        <v>0.2190601577796872</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2464389805935388</v>
+        <v>0.2483389805935388</v>
       </c>
       <c r="C92">
-        <v>-6.802153146483398</v>
+        <v>-6.98821001770731</v>
       </c>
       <c r="D92">
-        <v>4.099846853516601</v>
+        <v>4.06758998229269</v>
       </c>
       <c r="E92">
-        <v>12.062</v>
+        <v>12.2158</v>
       </c>
       <c r="F92">
-        <v>13.842</v>
+        <v>13.9958</v>
       </c>
       <c r="G92">
         <v>2.94</v>
@@ -8819,37 +8819,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M92">
-        <v>3.2639436</v>
+        <v>3.30020964</v>
       </c>
       <c r="N92">
-        <v>-2.548943599999999</v>
+        <v>-2.58520964</v>
       </c>
       <c r="O92">
-        <v>-0.4078309759999999</v>
+        <v>-0.4136335423999999</v>
       </c>
       <c r="P92">
-        <v>-2.141112623999999</v>
+        <v>-2.1715760976</v>
       </c>
       <c r="Q92">
-        <v>-1.766112623999999</v>
+        <v>-1.7965760976</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4165721206297966</v>
+        <v>0.4577690229219962</v>
       </c>
       <c r="T92">
-        <v>5.103817800942839</v>
+        <v>5.670908667714267</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.03504962524474995</v>
+        <v>0.03466446452777467</v>
       </c>
       <c r="W92">
-        <v>0.227535298367288</v>
+        <v>0.2276261192643507</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2190601577796872</v>
+        <v>0.2166529032985918</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2483389805935388</v>
+        <v>0.2502389805935388</v>
       </c>
       <c r="C93">
-        <v>-6.98821001770731</v>
+        <v>-7.173763268591332</v>
       </c>
       <c r="D93">
-        <v>4.06758998229269</v>
+        <v>4.035836731408668</v>
       </c>
       <c r="E93">
-        <v>12.2158</v>
+        <v>12.3696</v>
       </c>
       <c r="F93">
-        <v>13.9958</v>
+        <v>14.1496</v>
       </c>
       <c r="G93">
         <v>2.94</v>
@@ -8901,37 +8901,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M93">
-        <v>3.30020964</v>
+        <v>3.33647568</v>
       </c>
       <c r="N93">
-        <v>-2.58520964</v>
+        <v>-2.62147568</v>
       </c>
       <c r="O93">
-        <v>-0.4136335423999999</v>
+        <v>-0.4194361087999999</v>
       </c>
       <c r="P93">
-        <v>-2.1715760976</v>
+        <v>-2.2020395712</v>
       </c>
       <c r="Q93">
-        <v>-1.7965760976</v>
+        <v>-1.8270395712</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4577690229219962</v>
+        <v>0.5092651507872459</v>
       </c>
       <c r="T93">
-        <v>5.670908667714267</v>
+        <v>6.379772251178552</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03466446452777467</v>
+        <v>0.03428767686986407</v>
       </c>
       <c r="W93">
-        <v>0.2276261192643507</v>
+        <v>0.227714965794086</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2166529032985918</v>
+        <v>0.2142979804366505</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2502389805935388</v>
+        <v>0.2521389805935388</v>
       </c>
       <c r="C94">
-        <v>-7.173763268591332</v>
+        <v>-7.358824602168434</v>
       </c>
       <c r="D94">
-        <v>4.035836731408668</v>
+        <v>4.004575397831565</v>
       </c>
       <c r="E94">
-        <v>12.3696</v>
+        <v>12.5234</v>
       </c>
       <c r="F94">
-        <v>14.1496</v>
+        <v>14.3034</v>
       </c>
       <c r="G94">
         <v>2.94</v>
@@ -8983,37 +8983,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M94">
-        <v>3.33647568</v>
+        <v>3.37274172</v>
       </c>
       <c r="N94">
-        <v>-2.62147568</v>
+        <v>-2.65774172</v>
       </c>
       <c r="O94">
-        <v>-0.4194361087999999</v>
+        <v>-0.4252386752</v>
       </c>
       <c r="P94">
-        <v>-2.2020395712</v>
+        <v>-2.2325030448</v>
       </c>
       <c r="Q94">
-        <v>-1.8270395712</v>
+        <v>-1.8575030448</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5092651507872459</v>
+        <v>0.5754744580425668</v>
       </c>
       <c r="T94">
-        <v>6.379772251178552</v>
+        <v>7.291168287061204</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03428767686986407</v>
+        <v>0.03391899217233866</v>
       </c>
       <c r="W94">
-        <v>0.227714965794086</v>
+        <v>0.2278019016457626</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2142979804366505</v>
+        <v>0.2119937010771167</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2521389805935388</v>
+        <v>0.2540389805935389</v>
       </c>
       <c r="C95">
-        <v>-7.358824602168434</v>
+        <v>-7.543405361654918</v>
       </c>
       <c r="D95">
-        <v>4.004575397831565</v>
+        <v>3.973794638345082</v>
       </c>
       <c r="E95">
-        <v>12.5234</v>
+        <v>12.6772</v>
       </c>
       <c r="F95">
-        <v>14.3034</v>
+        <v>14.4572</v>
       </c>
       <c r="G95">
         <v>2.94</v>
@@ -9065,37 +9065,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M95">
-        <v>3.37274172</v>
+        <v>3.40900776</v>
       </c>
       <c r="N95">
-        <v>-2.65774172</v>
+        <v>-2.69400776</v>
       </c>
       <c r="O95">
-        <v>-0.4252386752</v>
+        <v>-0.4310412416</v>
       </c>
       <c r="P95">
-        <v>-2.2325030448</v>
+        <v>-2.2629665184</v>
       </c>
       <c r="Q95">
-        <v>-1.8575030448</v>
+        <v>-1.8879665184</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5754744580425668</v>
+        <v>0.6637535343829948</v>
       </c>
       <c r="T95">
-        <v>7.291168287061204</v>
+        <v>8.506363001571406</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03391899217233866</v>
+        <v>0.03355815183007973</v>
       </c>
       <c r="W95">
-        <v>0.2278019016457626</v>
+        <v>0.2278869877984672</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2119937010771167</v>
+        <v>0.2097384489379984</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2540389805935389</v>
+        <v>0.2559389805935388</v>
       </c>
       <c r="C96">
-        <v>-7.543405361654918</v>
+        <v>-7.727516544173407</v>
       </c>
       <c r="D96">
-        <v>3.973794638345082</v>
+        <v>3.943483455826593</v>
       </c>
       <c r="E96">
-        <v>12.6772</v>
+        <v>12.831</v>
       </c>
       <c r="F96">
-        <v>14.4572</v>
+        <v>14.611</v>
       </c>
       <c r="G96">
         <v>2.94</v>
@@ -9147,37 +9147,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M96">
-        <v>3.40900776</v>
+        <v>3.4452738</v>
       </c>
       <c r="N96">
-        <v>-2.69400776</v>
+        <v>-2.7302738</v>
       </c>
       <c r="O96">
-        <v>-0.4310412416</v>
+        <v>-0.436843808</v>
       </c>
       <c r="P96">
-        <v>-2.2629665184</v>
+        <v>-2.293429992</v>
       </c>
       <c r="Q96">
-        <v>-1.8879665184</v>
+        <v>-1.918429992</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6637535343829948</v>
+        <v>0.7873442412595941</v>
       </c>
       <c r="T96">
-        <v>8.506363001571406</v>
+        <v>10.20763560188569</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03355815183007973</v>
+        <v>0.0332049081266052</v>
       </c>
       <c r="W96">
-        <v>0.2278869877984672</v>
+        <v>0.2279702826637465</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2097384489379984</v>
+        <v>0.2075306757912826</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2559389805935388</v>
+        <v>0.2578389805935389</v>
       </c>
       <c r="C97">
-        <v>-7.727516544173407</v>
+        <v>-7.91116881385254</v>
       </c>
       <c r="D97">
-        <v>3.943483455826593</v>
+        <v>3.913631186147461</v>
       </c>
       <c r="E97">
-        <v>12.831</v>
+        <v>12.9848</v>
       </c>
       <c r="F97">
-        <v>14.611</v>
+        <v>14.7648</v>
       </c>
       <c r="G97">
         <v>2.94</v>
@@ -9229,37 +9229,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M97">
-        <v>3.4452738</v>
+        <v>3.48153984</v>
       </c>
       <c r="N97">
-        <v>-2.7302738</v>
+        <v>-2.76653984</v>
       </c>
       <c r="O97">
-        <v>-0.436843808</v>
+        <v>-0.4426463744</v>
       </c>
       <c r="P97">
-        <v>-2.293429992</v>
+        <v>-2.3238934656</v>
       </c>
       <c r="Q97">
-        <v>-1.918429992</v>
+        <v>-1.9488934656</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7873442412595941</v>
+        <v>0.9727303015744931</v>
       </c>
       <c r="T97">
-        <v>10.20763560188569</v>
+        <v>12.75954450235712</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0332049081266052</v>
+        <v>0.03285902366695307</v>
       </c>
       <c r="W97">
-        <v>0.2279702826637465</v>
+        <v>0.2280518422193325</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2075306757912826</v>
+        <v>0.2053688979184567</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2578389805935388</v>
+        <v>0.2597389805935388</v>
       </c>
       <c r="C98">
-        <v>-7.911168813852538</v>
+        <v>-8.094372514336129</v>
       </c>
       <c r="D98">
-        <v>3.913631186147461</v>
+        <v>3.884227485663868</v>
       </c>
       <c r="E98">
-        <v>12.9848</v>
+        <v>13.1386</v>
       </c>
       <c r="F98">
-        <v>14.7648</v>
+        <v>14.9186</v>
       </c>
       <c r="G98">
         <v>2.94</v>
@@ -9311,37 +9311,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M98">
-        <v>3.48153984</v>
+        <v>3.51780588</v>
       </c>
       <c r="N98">
-        <v>-2.76653984</v>
+        <v>-2.802805879999999</v>
       </c>
       <c r="O98">
-        <v>-0.4426463744</v>
+        <v>-0.4484489407999999</v>
       </c>
       <c r="P98">
-        <v>-2.3238934656</v>
+        <v>-2.354356939199999</v>
       </c>
       <c r="Q98">
-        <v>-1.9488934656</v>
+        <v>-1.979356939199999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9727303015744906</v>
+        <v>1.281707068765988</v>
       </c>
       <c r="T98">
-        <v>12.75954450235709</v>
+        <v>17.01272600314278</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03285902366695307</v>
+        <v>0.03252027084564428</v>
       </c>
       <c r="W98">
-        <v>0.2280518422193325</v>
+        <v>0.2281317201345971</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2053688979184567</v>
+        <v>0.2032516927852768</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2597389805935388</v>
+        <v>0.2616389805935388</v>
       </c>
       <c r="C99">
-        <v>-8.094372514336129</v>
+        <v>-8.277137680732665</v>
       </c>
       <c r="D99">
-        <v>3.884227485663868</v>
+        <v>3.855262319267335</v>
       </c>
       <c r="E99">
-        <v>13.1386</v>
+        <v>13.2924</v>
       </c>
       <c r="F99">
-        <v>14.9186</v>
+        <v>15.0724</v>
       </c>
       <c r="G99">
         <v>2.94</v>
@@ -9393,37 +9393,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M99">
-        <v>3.51780588</v>
+        <v>3.55407192</v>
       </c>
       <c r="N99">
-        <v>-2.802805879999999</v>
+        <v>-2.839071919999999</v>
       </c>
       <c r="O99">
-        <v>-0.4484489407999999</v>
+        <v>-0.4542515071999999</v>
       </c>
       <c r="P99">
-        <v>-2.354356939199999</v>
+        <v>-2.384820412799999</v>
       </c>
       <c r="Q99">
-        <v>-1.979356939199999</v>
+        <v>-2.009820412799999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.281707068765988</v>
+        <v>1.899660603148981</v>
       </c>
       <c r="T99">
-        <v>17.01272600314278</v>
+        <v>25.51908900471417</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03252027084564428</v>
+        <v>0.03218843134721934</v>
       </c>
       <c r="W99">
-        <v>0.2281317201345971</v>
+        <v>0.2282099678883257</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2032516927852768</v>
+        <v>0.2011776959201209</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2616389805935388</v>
+        <v>0.2635389805935389</v>
       </c>
       <c r="C100">
-        <v>-8.277137680732665</v>
+        <v>-8.459474051034052</v>
       </c>
       <c r="D100">
-        <v>3.855262319267335</v>
+        <v>3.826725948965947</v>
       </c>
       <c r="E100">
-        <v>13.2924</v>
+        <v>13.4462</v>
       </c>
       <c r="F100">
-        <v>15.0724</v>
+        <v>15.2262</v>
       </c>
       <c r="G100">
         <v>2.94</v>
@@ -9475,37 +9475,37 @@
         <v>0.7150000000000001</v>
       </c>
       <c r="M100">
-        <v>3.55407192</v>
+        <v>3.59033796</v>
       </c>
       <c r="N100">
-        <v>-2.839071919999999</v>
+        <v>-2.87533796</v>
       </c>
       <c r="O100">
-        <v>-0.4542515071999999</v>
+        <v>-0.4600540735999999</v>
       </c>
       <c r="P100">
-        <v>-2.384820412799999</v>
+        <v>-2.4152838864</v>
       </c>
       <c r="Q100">
-        <v>-2.009820412799999</v>
+        <v>-2.0402838864</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.899660603148981</v>
+        <v>3.753521206297962</v>
       </c>
       <c r="T100">
-        <v>25.51908900471417</v>
+        <v>51.03817800942835</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03218843134721934</v>
+        <v>0.03186329567704541</v>
       </c>
       <c r="W100">
-        <v>0.2282099678883257</v>
+        <v>0.2282866348793527</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2011776959201209</v>
+        <v>0.1991455979815339</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2635389805935389</v>
-      </c>
-      <c r="C101">
-        <v>-8.459474051034052</v>
-      </c>
-      <c r="D101">
-        <v>3.826725948965947</v>
-      </c>
-      <c r="E101">
-        <v>13.4462</v>
-      </c>
-      <c r="F101">
-        <v>15.2262</v>
-      </c>
-      <c r="G101">
-        <v>2.94</v>
-      </c>
-      <c r="H101">
-        <v>13.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.09</v>
-      </c>
-      <c r="K101">
-        <v>0.375</v>
-      </c>
-      <c r="L101">
-        <v>0.7150000000000001</v>
-      </c>
-      <c r="M101">
-        <v>3.59033796</v>
-      </c>
-      <c r="N101">
-        <v>-2.87533796</v>
-      </c>
-      <c r="O101">
-        <v>-0.4600540735999999</v>
-      </c>
-      <c r="P101">
-        <v>-2.4152838864</v>
-      </c>
-      <c r="Q101">
-        <v>-2.0402838864</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.753521206297962</v>
-      </c>
-      <c r="T101">
-        <v>51.03817800942835</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.03186329567704541</v>
-      </c>
-      <c r="W101">
-        <v>0.2282866348793527</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1991455979815339</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
